--- a/m7_year1_master_by_topic.xlsx
+++ b/m7_year1_master_by_topic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master – By Topic" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Master – By Topic" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,13 @@
     <font>
       <color rgb="00BBBBBB"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -137,6 +142,11 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -197,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -375,6 +385,90 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -741,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -754,6 +848,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -821,1942 +917,2451 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="K3" s="62" t="inlineStr">
+        <is>
+          <t>Free Resources (YouTube / MOOCs)</t>
+        </is>
+      </c>
+      <c r="L3" s="62" t="inlineStr">
+        <is>
+          <t>Paid Resources (HBS Online / Coursera)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="64" t="inlineStr">
         <is>
           <t>Financial Reporting and Control (FRC)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="64" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="64" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="64" t="inlineStr">
         <is>
           <t>Accounting &amp; Management</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="64" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="64" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>Accounting fundamentals: how to read, interpret, and use financial statements; managerial control systems.</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="J4" s="64" t="inlineStr"/>
+      <c r="K4" s="65" t="inlineStr">
+        <is>
+          <t>Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+MIT OCW Financial Accounting 15.515 (ocw.mit.edu/courses/15-515-financial-accounting-fall-2003/)
+Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)
+Farhat Accounting Lectures (YT: search 'Farhat Lectures')</t>
+        </is>
+      </c>
+      <c r="L4" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+HBS Online CORe Bundle ~$2,650 – includes Financial Accounting (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="66" t="n"/>
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>Financial Accounting</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="64" t="inlineStr">
         <is>
           <t>15.501 / 15.516</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="64" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="64" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="64" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="64" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>Reading/interpreting financial statements; accrual accounting, revenue recognition, balance-sheet analysis.</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
+      <c r="J5" s="64" t="inlineStr"/>
+      <c r="K5" s="65" t="inlineStr">
+        <is>
+          <t>Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+MIT OCW Financial Accounting 15.515 (ocw.mit.edu/courses/15-515-financial-accounting-fall-2003/)
+Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)</t>
+        </is>
+      </c>
+      <c r="L5" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="66" t="n"/>
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>Financial Accounting</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="64" t="inlineStr">
         <is>
           <t>ACCT 210</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="64" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="64" t="inlineStr">
         <is>
           <t>Analytical Foundations</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="64" t="inlineStr">
         <is>
           <t>4 units</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="64" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>How economic activities map into financial statements; balance sheets, income statements, cash flow.</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
+      <c r="J6" s="64" t="inlineStr"/>
+      <c r="K6" s="65" t="inlineStr">
+        <is>
+          <t>Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+MIT OCW Financial Accounting 15.515 (ocw.mit.edu/courses/15-515-financial-accounting-fall-2003/)
+Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)</t>
+        </is>
+      </c>
+      <c r="L6" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="67" t="n"/>
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>Managerial Accounting</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>ACCT 219</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="64" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="64" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="64" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>Using accounting information for internal decisions: cost accounting, budgeting, performance measurement.</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="64" t="inlineStr"/>
+      <c r="K7" s="65" t="inlineStr">
+        <is>
+          <t>Edspira – Managerial Accounting series (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+Farhat Accounting Lectures – Managerial Accounting (YT: search 'Farhat Lectures')
+Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)</t>
+        </is>
+      </c>
+      <c r="L7" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="69" t="inlineStr">
         <is>
           <t>Finance I</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="69" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="69" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="69" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="69" t="inlineStr">
         <is>
           <t>Foundations of financial analysis: valuation, capital markets, cost of capital, investment decisions.</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr"/>
+      <c r="J8" s="69" t="inlineStr"/>
+      <c r="K8" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Corporate Finance Full Course (YT: youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw)
+Patrick Boyle – On Finance (YT: youtube.com/@PBoyle)
+Corporate Finance Institute – CFI (YT: youtube.com/channel/UCGtbVv_ACgV7difdVZ92NMw)
+Khan Academy – Finance (khanacademy.org/economics-finance-domain/core-finance)</t>
+        </is>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
+HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="A9" s="66" t="n"/>
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="69" t="inlineStr">
         <is>
           <t>Finance II</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="69" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="69" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="69" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="69" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="69" t="inlineStr">
         <is>
           <t>Advanced topics: capital structure, M&amp;A, corporate governance, financial policy.</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr"/>
+      <c r="J9" s="69" t="inlineStr"/>
+      <c r="K9" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Valuation Full Course (YT: youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw)
+Patrick Boyle – On Finance (YT: youtube.com/@PBoyle)
+Corporate Finance Institute – CFI (YT: youtube.com/channel/UCGtbVv_ACgV7difdVZ92NMw)</t>
+        </is>
+      </c>
+      <c r="L9" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="A10" s="66" t="n"/>
+      <c r="B10" s="69" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="69" t="inlineStr">
         <is>
           <t>Managerial Finance</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="69" t="inlineStr">
         <is>
           <t>15.401</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="69" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="69" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="69" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="69" t="inlineStr">
         <is>
           <t>Core Elective (choose 1 of 4)</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="69" t="inlineStr">
         <is>
           <t>Corporate finance fundamentals: capital budgeting, valuation, risk, capital structure, financial markets.</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="69" t="inlineStr">
         <is>
           <t>One of 4 Sem-1 'core electives'</t>
         </is>
       </c>
+      <c r="K10" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Corporate Finance Full Course (YT: youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw)
+Patrick Boyle – On Finance (YT: youtube.com/@PBoyle)
+Corporate Finance Institute – CFI (YT: youtube.com/channel/UCGtbVv_ACgV7difdVZ92NMw)</t>
+        </is>
+      </c>
+      <c r="L10" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
+Wharton Finance on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="67" t="n"/>
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="69" t="inlineStr">
         <is>
           <t>Corporate Finance</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="69" t="inlineStr">
         <is>
           <t>FINANCE 229</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="69" t="inlineStr">
         <is>
           <t>Winter</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="69" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="69" t="inlineStr">
         <is>
           <t>4 units</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="69" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="69" t="inlineStr">
         <is>
           <t>Capital budgeting, valuation, risk and return, capital structure, corporate financial policy.</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr"/>
+      <c r="J11" s="69" t="inlineStr"/>
+      <c r="K11" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Valuation MBA Spring 2025 (YT: youtube.com/playlist?list=PLUkh9m2BorqkgpNyRpP-NL3BS4yvFabXk)
+Patrick Boyle – On Finance (YT: youtube.com/@PBoyle)
+Corporate Finance Institute – CFI (YT: youtube.com/channel/UCGtbVv_ACgV7difdVZ92NMw)</t>
+        </is>
+      </c>
+      <c r="L11" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
+Wharton Finance on Coursera – free audit / $49 cert (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>Economics, Government &amp; Global Economy</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>Business, Government, and the International Economy (BGIE)</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="71" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="71" t="inlineStr">
         <is>
           <t>Economics &amp; Policy</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="71" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="71" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="71" t="inlineStr">
         <is>
           <t>Macroeconomics, trade policy, currency markets, political economy of business in a global context.</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="71" t="inlineStr">
         <is>
           <t>Macro / political economy</t>
         </is>
       </c>
+      <c r="K12" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Micro + Macro (mru.org / YT: youtube.com/channel/UCnkEhPBMZcEO0QGu51fDFDg)
+Freakonomics Radio Podcast – applied economics (freakonomics.com)
+Economics Explained (YT: youtube.com/c/EconomicsExplained)
+Khan Academy Macroeconomics (khanacademy.org/economics-finance-domain/macroeconomics)</t>
+        </is>
+      </c>
+      <c r="L12" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="66" t="n"/>
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>Economic Analysis for Business Decisions</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>15.010 / 15.011</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="71" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="71" t="inlineStr">
         <is>
           <t>Microeconomics</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="71" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="71" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="71" t="inlineStr">
         <is>
           <t>Applied micro: market structure, pricing, supply &amp; demand, game theory, strategic interaction.</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="J13" s="71" t="inlineStr">
         <is>
           <t>Micro</t>
         </is>
       </c>
+      <c r="K13" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Microeconomics (mru.org)
+Khan Academy Microeconomics (khanacademy.org/economics-finance-domain/microeconomics)
+Freakonomics Radio Podcast (freakonomics.com)</t>
+        </is>
+      </c>
+      <c r="L13" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="A14" s="66" t="n"/>
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="71" t="inlineStr">
         <is>
           <t>Microeconomics</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="71" t="inlineStr">
         <is>
           <t>MGTECON 209</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="71" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="71" t="inlineStr">
         <is>
           <t>Analytical Foundations</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="71" t="inlineStr">
         <is>
           <t>4 units</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="71" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="71" t="inlineStr">
         <is>
           <t>Microeconomics for managerial decision-making: markets, pricing, game theory, strategic interaction.</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J14" s="71" t="inlineStr">
         <is>
           <t>Micro</t>
         </is>
       </c>
+      <c r="K14" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Microeconomics (mru.org/courses/principles-of-microeconomics)
+Khan Academy Microeconomics (khanacademy.org/economics-finance-domain/microeconomics)</t>
+        </is>
+      </c>
+      <c r="L14" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="A15" s="66" t="n"/>
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="71" t="inlineStr">
         <is>
           <t>Macroeconomics</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="71" t="inlineStr">
         <is>
           <t>MGTECON 240</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="71" t="inlineStr">
         <is>
           <t>Winter</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="71" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="71" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="71" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="71" t="inlineStr">
         <is>
           <t>Macro environment: GDP, inflation, interest/exchange rates, monetary and fiscal policy.</t>
         </is>
       </c>
-      <c r="J15" s="13" t="inlineStr">
+      <c r="J15" s="71" t="inlineStr">
         <is>
           <t>Macro</t>
         </is>
       </c>
+      <c r="K15" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Macroeconomics (mru.org/courses/principles-of-macroeconomics)
+Economics Explained (YT: youtube.com/c/EconomicsExplained)
+Khan Academy Macroeconomics (khanacademy.org/economics-finance-domain/macroeconomics)</t>
+        </is>
+      </c>
+      <c r="L15" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="A16" s="67" t="n"/>
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="71" t="inlineStr">
         <is>
           <t>Strategy Beyond Markets</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>POLECON 239</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="71" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="71" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="71" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="71" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="71" t="inlineStr">
         <is>
           <t>Political economy of business: lobbying, regulation, non-market strategy, business–government intersection.</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="71" t="inlineStr">
         <is>
           <t>Non-market / political economy</t>
         </is>
       </c>
+      <c r="K16" s="65" t="inlineStr">
+        <is>
+          <t>Freakonomics Radio – business &amp; political economy episodes (freakonomics.com)
+HBS Cold Call Podcast – ethics &amp; policy cases (hbr.org/2019/04/podcast-cold-call)
+HBR IdeaCast Podcast (hbr.org/podcasts)</t>
+        </is>
+      </c>
+      <c r="L16" s="65" t="inlineStr">
+        <is>
+          <t>— (no direct HBS Online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="73" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="73" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="73" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="73" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="73" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="73" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="73" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="73" t="inlineStr">
         <is>
           <t>Core frameworks: customer analysis, segmentation, targeting, positioning, the marketing mix.</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr"/>
+      <c r="J17" s="73" t="inlineStr"/>
+      <c r="K17" s="65" t="inlineStr">
+        <is>
+          <t>HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
+Neil Patel – Digital Marketing Strategy (YT: youtube.com/neilpatel)
+Wharton Marketing on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="L17" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)
+Wharton Marketing on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="A18" s="66" t="n"/>
+      <c r="B18" s="73" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="73" t="inlineStr">
         <is>
           <t>Marketing Innovation</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="73" t="inlineStr">
         <is>
           <t>15.814</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="73" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="73" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="73" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="73" t="inlineStr">
         <is>
           <t>Core Elective (choose 1 of 4)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I18" s="73" t="inlineStr">
         <is>
           <t>Marketing strategy: consumer behavior, segmentation, positioning, product development, go-to-market.</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J18" s="73" t="inlineStr">
         <is>
           <t>One of 4 Sem-1 'core electives'</t>
         </is>
       </c>
+      <c r="K18" s="65" t="inlineStr">
+        <is>
+          <t>HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
+Neil Patel – Digital Marketing Strategy (YT: youtube.com/neilpatel)
+Wharton Marketing on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="L18" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="A19" s="67" t="n"/>
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="73" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="73" t="inlineStr">
         <is>
           <t>MKTG 249</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="73" t="inlineStr">
         <is>
           <t>Winter</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="73" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="73" t="inlineStr">
         <is>
           <t>3–4 units</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="73" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="73" t="inlineStr">
         <is>
           <t>Marketing strategy: consumer behavior, segmentation, targeting, positioning, brand, marketing mix.</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr"/>
+      <c r="J19" s="73" t="inlineStr"/>
+      <c r="K19" s="65" t="inlineStr">
+        <is>
+          <t>HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
+Neil Patel – Digital Marketing Strategy (YT: youtube.com/neilpatel)</t>
+        </is>
+      </c>
+      <c r="L19" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)
+Wharton Marketing on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="74" t="inlineStr">
         <is>
           <t>Operations &amp; Technology Management</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="75" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="75" t="inlineStr">
         <is>
           <t>Technology and Operations Management (TOM)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="75" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="75" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="75" t="inlineStr">
         <is>
           <t>Technology &amp; Operations</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="75" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="75" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>Process design, supply chain, quality management, and the role of technology in operations.</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr"/>
+      <c r="J20" s="75" t="inlineStr"/>
+      <c r="K20" s="65" t="inlineStr">
+        <is>
+          <t>MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
+Wharton Operations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="L20" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)
+Wharton Operations on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="A21" s="66" t="n"/>
+      <c r="B21" s="75" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="75" t="inlineStr">
         <is>
           <t>Introduction to Operations Management</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="75" t="inlineStr">
         <is>
           <t>15.761</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="75" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="75" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="75" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="75" t="inlineStr">
         <is>
           <t>Core Elective (choose 1 of 4)</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>Process analysis, queuing, inventory, supply chain design, quality management.</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="75" t="inlineStr">
         <is>
           <t>One of 4 Sem-1 'core electives'</t>
         </is>
       </c>
+      <c r="K21" s="65" t="inlineStr">
+        <is>
+          <t>MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
+Wharton Operations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="L21" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)
+Wharton Operations on Coursera ~$49 cert</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="A22" s="67" t="n"/>
+      <c r="B22" s="75" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="75" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="75" t="inlineStr">
         <is>
           <t>OIT 262</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="75" t="inlineStr">
         <is>
           <t>Winter</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="75" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="75" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="75" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>Process analysis, capacity management, inventory, supply chains, quality fundamentals.</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr"/>
+      <c r="J22" s="75" t="inlineStr"/>
+      <c r="K22" s="65" t="inlineStr">
+        <is>
+          <t>MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
+Wharton Operations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="L22" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>Data, Analytics, AI &amp; Information Systems</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="77" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="77" t="inlineStr">
         <is>
           <t>Data Science and AI for Leaders (DSAIL)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="77" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="77" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="77" t="inlineStr">
         <is>
           <t>Technology &amp; Analytics</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="77" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="77" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="77" t="inlineStr">
         <is>
           <t>AI tools, data-science fundamentals, applying AI to business decisions.</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J23" s="77" t="inlineStr">
         <is>
           <t>NEW (2025) – first AI-native required course at HBS; Class of 2027</t>
         </is>
       </c>
+      <c r="K23" s="65" t="inlineStr">
+        <is>
+          <t>Alex The Analyst – Full Data Analyst Bootcamp (YT: youtube.com/@AlexTheAnalyst)
+StatQuest with Josh Starmer – ML &amp; Stats (YT: youtube.com/c/joshstarmer)
+365 Data Science YouTube (youtube.com/c/365DataScience)</t>
+        </is>
+      </c>
+      <c r="L23" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)
+HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="A24" s="66" t="n"/>
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="77" t="inlineStr">
         <is>
           <t>Data, Models and Decisions</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="77" t="inlineStr">
         <is>
           <t>15.060</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="77" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="77" t="inlineStr">
         <is>
           <t>Statistics / Analytics</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="77" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="77" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="77" t="inlineStr">
         <is>
           <t>Quantitative decision-making: probability, regression, simulation, optimization.</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr"/>
+      <c r="J24" s="77" t="inlineStr"/>
+      <c r="K24" s="65" t="inlineStr">
+        <is>
+          <t>StatQuest with Josh Starmer – Statistics &amp; ML (YT: youtube.com/c/joshstarmer)
+Alex The Analyst (YT: youtube.com/@AlexTheAnalyst)
+Khan Academy Statistics &amp; Probability (khanacademy.org/math/statistics-probability)</t>
+        </is>
+      </c>
+      <c r="L24" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)
+HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="A25" s="66" t="n"/>
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="77" t="inlineStr">
         <is>
           <t>Data Analysis and Decision Making (Base / Accelerated)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="77" t="inlineStr">
         <is>
           <t>OB 358 / OB 360</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="77" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="77" t="inlineStr">
         <is>
           <t>Analytical Foundations</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="77" t="inlineStr">
         <is>
           <t>4 units</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="77" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="77" t="inlineStr">
         <is>
           <t>Probability, sampling, hypothesis testing, regression, basic ML prediction. Placed by assessment.</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J25" s="77" t="inlineStr">
         <is>
           <t>Base vs Accelerated track</t>
         </is>
       </c>
+      <c r="K25" s="65" t="inlineStr">
+        <is>
+          <t>StatQuest with Josh Starmer (YT: youtube.com/c/joshstarmer)
+Alex The Analyst (YT: youtube.com/@AlexTheAnalyst)
+Khan Academy Statistics (khanacademy.org/math/statistics-probability)</t>
+        </is>
+      </c>
+      <c r="L25" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="A26" s="66" t="n"/>
+      <c r="B26" s="77" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="77" t="inlineStr">
         <is>
           <t>Optimization and Simulation Modeling</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="77" t="inlineStr">
         <is>
           <t>MS&amp;E 348</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="77" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="77" t="inlineStr">
         <is>
           <t>Analytical Foundations</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="77" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H26" s="77" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="77" t="inlineStr">
         <is>
           <t>Linear/integer programming, simulation, decision analysis for business optimization.</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr"/>
+      <c r="J26" s="77" t="inlineStr"/>
+      <c r="K26" s="65" t="inlineStr">
+        <is>
+          <t>StatQuest with Josh Starmer – ML/optimization concepts (YT: youtube.com/c/joshstarmer)
+365 Data Science (YT: youtube.com/c/365DataScience)</t>
+        </is>
+      </c>
+      <c r="L26" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="A27" s="67" t="n"/>
+      <c r="B27" s="77" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="77" t="inlineStr">
         <is>
           <t>Information Management</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="77" t="inlineStr">
         <is>
           <t>OIT 335</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="77" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="77" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="77" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="77" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="77" t="inlineStr">
         <is>
           <t>IT strategy, digital platforms, data management, role of information systems in business.</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr"/>
+      <c r="J27" s="77" t="inlineStr"/>
+      <c r="K27" s="65" t="inlineStr">
+        <is>
+          <t>HBR IdeaCast – Digital transformation episodes (hbr.org/podcasts)
+Stanford GSB YouTube – technology strategy talks (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
+        </is>
+      </c>
+      <c r="L27" s="65" t="inlineStr">
+        <is>
+          <t>— (no direct HBS Online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="78" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="79" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="79" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="79" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="79" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="79" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H28" s="26" t="inlineStr">
+      <c r="H28" s="79" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I28" s="25" t="inlineStr">
+      <c r="I28" s="79" t="inlineStr">
         <is>
           <t>Competitive strategy frameworks: industry analysis, competitive advantage, positioning.</t>
         </is>
       </c>
-      <c r="J28" s="25" t="inlineStr"/>
+      <c r="J28" s="79" t="inlineStr"/>
+      <c r="K28" s="65" t="inlineStr">
+        <is>
+          <t>Modern MBA – case-method strategy deep dives (YT: youtube.com/c/ModernMBA)
+Acquired Podcast – company strategy histories (acquired.fm)
+HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)
+Stanford GSB YouTube (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
+        </is>
+      </c>
+      <c r="L28" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)
+HBS Online Core Business Essentials ~$2,650 – includes Strategy module (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="A29" s="66" t="n"/>
+      <c r="B29" s="79" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="79" t="inlineStr">
         <is>
           <t>Competitive Strategy</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="79" t="inlineStr">
         <is>
           <t>15.900</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="79" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="79" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="G29" s="79" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H29" s="26" t="inlineStr">
+      <c r="H29" s="79" t="inlineStr">
         <is>
           <t>Core Elective (choose 1 of 4)</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
+      <c r="I29" s="79" t="inlineStr">
         <is>
           <t>Industry analysis, competitive positioning, strategic planning, dynamic strategy.</t>
         </is>
       </c>
-      <c r="J29" s="25" t="inlineStr">
+      <c r="J29" s="79" t="inlineStr">
         <is>
           <t>One of 4 Sem-1 'core electives'</t>
         </is>
       </c>
+      <c r="K29" s="65" t="inlineStr">
+        <is>
+          <t>Modern MBA (YT: youtube.com/c/ModernMBA)
+Acquired Podcast (acquired.fm)
+HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)</t>
+        </is>
+      </c>
+      <c r="L29" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)
+Wharton Business Foundations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="A30" s="67" t="n"/>
+      <c r="B30" s="79" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="79" t="inlineStr">
         <is>
           <t>Strategic Leadership</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="79" t="inlineStr">
         <is>
           <t>STRAMGT 259</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="79" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="79" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G30" s="25" t="inlineStr">
+      <c r="G30" s="79" t="inlineStr">
         <is>
           <t>3–4 units</t>
         </is>
       </c>
-      <c r="H30" s="26" t="inlineStr">
+      <c r="H30" s="79" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I30" s="79" t="inlineStr">
         <is>
           <t>Integrative: competitive strategy, industry analysis, leadership in executing strategy. Bridge to Year 2.</t>
         </is>
       </c>
-      <c r="J30" s="25" t="inlineStr"/>
+      <c r="J30" s="79" t="inlineStr"/>
+      <c r="K30" s="65" t="inlineStr">
+        <is>
+          <t>Modern MBA (YT: youtube.com/c/ModernMBA)
+Stanford GSB YouTube – strategy talks (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)
+HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)</t>
+        </is>
+      </c>
+      <c r="L30" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="80" t="inlineStr">
         <is>
           <t>Organizational Behavior, Leadership &amp; People</t>
         </is>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="81" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="81" t="inlineStr">
         <is>
           <t>Leadership and Organizational Behavior (LEAD)</t>
         </is>
       </c>
-      <c r="D31" s="28" t="inlineStr">
+      <c r="D31" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="81" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="81" t="inlineStr">
         <is>
           <t>Organizational Behavior</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="81" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H31" s="29" t="inlineStr">
+      <c r="H31" s="81" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I31" s="81" t="inlineStr">
         <is>
           <t>Individual/group behavior: motivation, team dynamics, leadership styles, organizational culture.</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr"/>
+      <c r="J31" s="81" t="inlineStr"/>
+      <c r="K31" s="65" t="inlineStr">
+        <is>
+          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)
+Stanford GSB YouTube (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)
+HBR IdeaCast Podcast (hbr.org/podcasts)
+TED Business (YT: youtube.com/c/TEDBusiness)</t>
+        </is>
+      </c>
+      <c r="L31" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)
+HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="A32" s="66" t="n"/>
+      <c r="B32" s="81" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="81" t="inlineStr">
         <is>
           <t>Organizational Processes</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D32" s="81" t="inlineStr">
         <is>
           <t>15.311</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="81" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="81" t="inlineStr">
         <is>
           <t>Org Behavior / Management</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="81" t="inlineStr">
         <is>
           <t>9 units</t>
         </is>
       </c>
-      <c r="H32" s="29" t="inlineStr">
+      <c r="H32" s="81" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I32" s="81" t="inlineStr">
         <is>
           <t>How organizations function: decision-making, culture, change management, leadership, human capital.</t>
         </is>
       </c>
-      <c r="J32" s="28" t="inlineStr"/>
+      <c r="J32" s="81" t="inlineStr"/>
+      <c r="K32" s="65" t="inlineStr">
+        <is>
+          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)
+HBR IdeaCast Podcast (hbr.org/podcasts)</t>
+        </is>
+      </c>
+      <c r="L32" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)
+HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="A33" s="66" t="n"/>
+      <c r="B33" s="81" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
+      <c r="C33" s="81" t="inlineStr">
         <is>
           <t>Organizational Behavior / Managing Groups and Teams</t>
         </is>
       </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="D33" s="81" t="inlineStr">
         <is>
           <t>OB 270 / GSBGEN 566</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="81" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="81" t="inlineStr">
         <is>
           <t>Leadership Foundations</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="81" t="inlineStr">
         <is>
           <t>3–4 units</t>
         </is>
       </c>
-      <c r="H33" s="29" t="inlineStr">
+      <c r="H33" s="81" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="I33" s="81" t="inlineStr">
         <is>
           <t>Behavioral foundations: motivation, team dynamics, leadership, culture; team performance &amp; group decisions.</t>
         </is>
       </c>
-      <c r="J33" s="28" t="inlineStr"/>
+      <c r="J33" s="81" t="inlineStr"/>
+      <c r="K33" s="65" t="inlineStr">
+        <is>
+          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)
+Stanford GSB YouTube (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)
+TED Business (YT: youtube.com/c/TEDBusiness)</t>
+        </is>
+      </c>
+      <c r="L33" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="A34" s="67" t="n"/>
+      <c r="B34" s="81" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="81" t="inlineStr">
         <is>
           <t>Human Resource Management</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="81" t="inlineStr">
         <is>
           <t>GSBGEN 518</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="81" t="inlineStr">
         <is>
           <t>Winter</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="81" t="inlineStr">
         <is>
           <t>Management Foundations</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="81" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H34" s="29" t="inlineStr">
+      <c r="H34" s="81" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
+      <c r="I34" s="81" t="inlineStr">
         <is>
           <t>Talent acquisition, performance management, compensation, org design, HR strategy.</t>
         </is>
       </c>
-      <c r="J34" s="28" t="inlineStr"/>
+      <c r="J34" s="81" t="inlineStr"/>
+      <c r="K34" s="65" t="inlineStr">
+        <is>
+          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+HBR IdeaCast Podcast – people &amp; talent episodes (hbr.org/podcasts)</t>
+        </is>
+      </c>
+      <c r="L34" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="82" t="inlineStr">
         <is>
           <t>Ethics, Accountability &amp; Social Purpose</t>
         </is>
       </c>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="83" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C35" s="83" t="inlineStr">
         <is>
           <t>Leadership and Corporate Accountability (LCA)</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="D35" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="83" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
+      <c r="F35" s="83" t="inlineStr">
         <is>
           <t>Ethics &amp; Leadership</t>
         </is>
       </c>
-      <c r="G35" s="31" t="inlineStr">
+      <c r="G35" s="83" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H35" s="32" t="inlineStr">
+      <c r="H35" s="83" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I35" s="31" t="inlineStr">
+      <c r="I35" s="83" t="inlineStr">
         <is>
           <t>Ethical decision-making, corporate responsibility, stakeholder management, legal dimensions of leadership.</t>
         </is>
       </c>
-      <c r="J35" s="31" t="inlineStr"/>
+      <c r="J35" s="83" t="inlineStr"/>
+      <c r="K35" s="65" t="inlineStr">
+        <is>
+          <t>HBS Cold Call Podcast – ethics cases (hbr.org/2019/04/podcast-cold-call)
+Edspira – Business Ethics module (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)
+HBR IdeaCast Podcast (hbr.org/podcasts)</t>
+        </is>
+      </c>
+      <c r="L35" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Negotiation Mastery ~$1,850 (online.hbs.edu/courses/negotiation)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="31" t="inlineStr">
+      <c r="A36" s="66" t="n"/>
+      <c r="B36" s="83" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
+      <c r="C36" s="83" t="inlineStr">
         <is>
           <t>Inclusion and Social Purpose of the Firm (SPF)</t>
         </is>
       </c>
-      <c r="D36" s="31" t="inlineStr">
+      <c r="D36" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="E36" s="83" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F36" s="31" t="inlineStr">
+      <c r="F36" s="83" t="inlineStr">
         <is>
           <t>General Management / Ethics</t>
         </is>
       </c>
-      <c r="G36" s="31" t="inlineStr">
+      <c r="G36" s="83" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H36" s="32" t="inlineStr">
+      <c r="H36" s="83" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I36" s="31" t="inlineStr">
+      <c r="I36" s="83" t="inlineStr">
         <is>
           <t>Two modules: diversity &amp; inclusion in the workplace + the firm's responsibility to society.</t>
         </is>
       </c>
-      <c r="J36" s="31" t="inlineStr">
+      <c r="J36" s="83" t="inlineStr">
         <is>
           <t>Two-module course</t>
         </is>
       </c>
+      <c r="K36" s="65" t="inlineStr">
+        <is>
+          <t>HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)
+HBR IdeaCast – CSR &amp; social purpose episodes (hbr.org/podcasts)
+TED Business – ethics talks (YT: youtube.com/c/TEDBusiness)</t>
+        </is>
+      </c>
+      <c r="L36" s="65" t="inlineStr">
+        <is>
+          <t>— (no direct HBS Online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="31" t="inlineStr">
+      <c r="A37" s="67" t="n"/>
+      <c r="B37" s="83" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C37" s="31" t="inlineStr">
+      <c r="C37" s="83" t="inlineStr">
         <is>
           <t>Leading with Values (Ethics)</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="D37" s="83" t="inlineStr">
         <is>
           <t>GSBGEN 567</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E37" s="83" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="F37" s="31" t="inlineStr">
+      <c r="F37" s="83" t="inlineStr">
         <is>
           <t>Leadership Foundations</t>
         </is>
       </c>
-      <c r="G37" s="31" t="inlineStr">
+      <c r="G37" s="83" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="H37" s="83" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I37" s="31" t="inlineStr">
+      <c r="I37" s="83" t="inlineStr">
         <is>
           <t>Ethical reasoning; frameworks for moral dilemmas; corporate responsibility; values-based leadership.</t>
         </is>
       </c>
-      <c r="J37" s="31" t="inlineStr"/>
+      <c r="J37" s="83" t="inlineStr"/>
+      <c r="K37" s="65" t="inlineStr">
+        <is>
+          <t>HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)
+TED Business (YT: youtube.com/c/TEDBusiness)
+HBR IdeaCast Podcast (hbr.org/podcasts)</t>
+        </is>
+      </c>
+      <c r="L37" s="65" t="inlineStr">
+        <is>
+          <t>— (no direct HBS Online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="33" t="inlineStr">
+      <c r="A38" s="84" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="85" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="85" t="inlineStr">
         <is>
           <t>The Entrepreneurial Manager (TEM)</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="D38" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="34" t="inlineStr">
+      <c r="E38" s="85" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F38" s="34" t="inlineStr">
+      <c r="F38" s="85" t="inlineStr">
         <is>
           <t>Entrepreneurial Management</t>
         </is>
       </c>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="G38" s="85" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H38" s="35" t="inlineStr">
+      <c r="H38" s="85" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I38" s="34" t="inlineStr">
+      <c r="I38" s="85" t="inlineStr">
         <is>
           <t>Entrepreneurial thinking for new ventures and within firms; opportunity recognition, resource acquisition.</t>
         </is>
       </c>
-      <c r="J38" s="34" t="inlineStr">
+      <c r="J38" s="85" t="inlineStr">
         <is>
           <t>Only school with required Y1 entrepreneurship</t>
         </is>
       </c>
+      <c r="K38" s="65" t="inlineStr">
+        <is>
+          <t>Y Combinator Startup School (YT: youtube.com/@ycombinator; startupschool.org/curriculum)
+Stanford eCorner – 2,000+ entrepreneur videos (ecorner.stanford.edu)
+HBS Cold Call Podcast – entrepreneurship episodes (hbr.org/2019/04/podcast-cold-call)</t>
+        </is>
+      </c>
+      <c r="L38" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Entrepreneurship Essentials ~$1,850 (online.hbs.edu/courses/entrepreneurship-essentials)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="86" t="inlineStr">
         <is>
           <t>Business Communication</t>
         </is>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="87" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="87" t="inlineStr">
         <is>
           <t>Communication for Leaders</t>
         </is>
       </c>
-      <c r="D39" s="37" t="inlineStr">
+      <c r="D39" s="87" t="inlineStr">
         <is>
           <t>15.280</t>
         </is>
       </c>
-      <c r="E39" s="37" t="inlineStr">
+      <c r="E39" s="87" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F39" s="37" t="inlineStr">
+      <c r="F39" s="87" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="G39" s="37" t="inlineStr">
+      <c r="G39" s="87" t="inlineStr">
         <is>
           <t>6 units</t>
         </is>
       </c>
-      <c r="H39" s="38" t="inlineStr">
+      <c r="H39" s="87" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I39" s="37" t="inlineStr">
+      <c r="I39" s="87" t="inlineStr">
         <is>
           <t>Written &amp; oral business communication: structuring arguments, presentations, memos, difficult conversations.</t>
         </is>
       </c>
-      <c r="J39" s="37" t="inlineStr">
+      <c r="J39" s="87" t="inlineStr">
         <is>
           <t>Only school with required Y1 communication</t>
         </is>
       </c>
+      <c r="K39" s="65" t="inlineStr">
+        <is>
+          <t>TED Business – communication &amp; presentation talks (YT: youtube.com/c/TEDBusiness)
+Stanford GSB YouTube – communication &amp; public speaking (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
+        </is>
+      </c>
+      <c r="L39" s="65" t="inlineStr">
+        <is>
+          <t>— (no direct HBS Online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="88" t="inlineStr">
         <is>
           <t>Experiential &amp; Global Immersion</t>
         </is>
       </c>
-      <c r="B40" s="40" t="inlineStr">
+      <c r="B40" s="89" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C40" s="40" t="inlineStr">
+      <c r="C40" s="89" t="inlineStr">
         <is>
           <t>FIELD Foundations (FIELD 1)</t>
         </is>
       </c>
-      <c r="D40" s="40" t="inlineStr">
+      <c r="D40" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="89" t="inlineStr">
         <is>
           <t>Term 1 (Fall)</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="89" t="inlineStr">
         <is>
           <t>Experiential / Leadership</t>
         </is>
       </c>
-      <c r="G40" s="40" t="inlineStr">
+      <c r="G40" s="89" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H40" s="41" t="inlineStr">
+      <c r="H40" s="89" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I40" s="40" t="inlineStr">
+      <c r="I40" s="89" t="inlineStr">
         <is>
           <t>Leadership development workshops, self-assessment, team exercises; preps for the Global Capstone.</t>
         </is>
       </c>
-      <c r="J40" s="40" t="inlineStr">
+      <c r="J40" s="89" t="inlineStr">
         <is>
           <t>FIELD program</t>
         </is>
       </c>
+      <c r="K40" s="65" t="inlineStr">
+        <is>
+          <t>— (experiential program; no direct online equivalent)</t>
+        </is>
+      </c>
+      <c r="L40" s="65" t="inlineStr">
+        <is>
+          <t>— (experiential program; no direct online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="40" t="inlineStr">
+      <c r="A41" s="66" t="n"/>
+      <c r="B41" s="89" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="C41" s="40" t="inlineStr">
+      <c r="C41" s="89" t="inlineStr">
         <is>
           <t>FIELD Global Capstone (FIELD 2)</t>
         </is>
       </c>
-      <c r="D41" s="40" t="inlineStr">
+      <c r="D41" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E41" s="40" t="inlineStr">
+      <c r="E41" s="89" t="inlineStr">
         <is>
           <t>Term 2 (Spring)</t>
         </is>
       </c>
-      <c r="F41" s="40" t="inlineStr">
+      <c r="F41" s="89" t="inlineStr">
         <is>
           <t>Experiential / Global</t>
         </is>
       </c>
-      <c r="G41" s="40" t="inlineStr">
+      <c r="G41" s="89" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H41" s="41" t="inlineStr">
+      <c r="H41" s="89" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I41" s="40" t="inlineStr">
+      <c r="I41" s="89" t="inlineStr">
         <is>
           <t>Teams partner with a global company to build a product/service; 6–14 day international immersion.</t>
         </is>
       </c>
-      <c r="J41" s="40" t="inlineStr">
+      <c r="J41" s="89" t="inlineStr">
         <is>
           <t>Destinations incl. Ghana, Japan, Saudi Arabia, India, etc.</t>
         </is>
       </c>
+      <c r="K41" s="65" t="inlineStr">
+        <is>
+          <t>— (experiential / global immersion; no direct online equivalent)</t>
+        </is>
+      </c>
+      <c r="L41" s="65" t="inlineStr">
+        <is>
+          <t>— (experiential / global immersion; no direct online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n"/>
-      <c r="B42" s="40" t="inlineStr">
+      <c r="A42" s="66" t="n"/>
+      <c r="B42" s="89" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
         </is>
       </c>
-      <c r="C42" s="40" t="inlineStr">
+      <c r="C42" s="89" t="inlineStr">
         <is>
           <t>Leadership Challenges for an Inclusive World (LEAD Week)</t>
         </is>
       </c>
-      <c r="D42" s="40" t="inlineStr">
+      <c r="D42" s="89" t="inlineStr">
         <is>
           <t>15.002</t>
         </is>
       </c>
-      <c r="E42" s="40" t="inlineStr">
+      <c r="E42" s="89" t="inlineStr">
         <is>
           <t>Fall (Sem 1)</t>
         </is>
       </c>
-      <c r="F42" s="40" t="inlineStr">
+      <c r="F42" s="89" t="inlineStr">
         <is>
           <t>Leadership / Inclusion</t>
         </is>
       </c>
-      <c r="G42" s="40" t="inlineStr">
+      <c r="G42" s="89" t="inlineStr">
         <is>
           <t>3 units</t>
         </is>
       </c>
-      <c r="H42" s="41" t="inlineStr">
+      <c r="H42" s="89" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I42" s="40" t="inlineStr">
+      <c r="I42" s="89" t="inlineStr">
         <is>
           <t>3-day immersive off-campus experience; workshops on leadership values, inclusive practices, integrity.</t>
         </is>
       </c>
-      <c r="J42" s="40" t="inlineStr">
+      <c r="J42" s="89" t="inlineStr">
         <is>
           <t>Mid-October; also inclusion-focused</t>
         </is>
       </c>
+      <c r="K42" s="65" t="inlineStr">
+        <is>
+          <t>HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)</t>
+        </is>
+      </c>
+      <c r="L42" s="65" t="inlineStr">
+        <is>
+          <t>— (immersive off-campus; no direct online equivalent)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n"/>
-      <c r="B43" s="40" t="inlineStr">
+      <c r="A43" s="66" t="n"/>
+      <c r="B43" s="89" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C43" s="40" t="inlineStr">
+      <c r="C43" s="89" t="inlineStr">
         <is>
           <t>Leadership Labs</t>
         </is>
       </c>
-      <c r="D43" s="40" t="inlineStr">
+      <c r="D43" s="89" t="inlineStr">
         <is>
           <t>GSBGEN</t>
         </is>
       </c>
-      <c r="E43" s="40" t="inlineStr">
+      <c r="E43" s="89" t="inlineStr">
         <is>
           <t>Autumn (Year 1)</t>
         </is>
       </c>
-      <c r="F43" s="40" t="inlineStr">
+      <c r="F43" s="89" t="inlineStr">
         <is>
           <t>Leadership Foundations</t>
         </is>
       </c>
-      <c r="G43" s="40" t="inlineStr">
+      <c r="G43" s="89" t="inlineStr">
         <is>
           <t>Non-credit / 1 unit</t>
         </is>
       </c>
-      <c r="H43" s="41" t="inlineStr">
+      <c r="H43" s="89" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I43" s="40" t="inlineStr">
+      <c r="I43" s="89" t="inlineStr">
         <is>
           <t>Small-group experiential workshops on self-awareness, interpersonal effectiveness, leadership style.</t>
         </is>
       </c>
-      <c r="J43" s="40" t="inlineStr">
+      <c r="J43" s="89" t="inlineStr">
         <is>
           <t>Coach-facilitated throughout Year 1</t>
         </is>
       </c>
+      <c r="K43" s="65" t="inlineStr">
+        <is>
+          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+Stanford GSB YouTube (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
+        </is>
+      </c>
+      <c r="L43" s="65" t="inlineStr">
+        <is>
+          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="A44" s="67" t="n"/>
+      <c r="B44" s="89" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
         </is>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C44" s="89" t="inlineStr">
         <is>
           <t>Global Experience Requirement (GER)</t>
         </is>
       </c>
-      <c r="D44" s="40" t="inlineStr">
+      <c r="D44" s="89" t="inlineStr">
         <is>
           <t>GSBGEN 580+</t>
         </is>
       </c>
-      <c r="E44" s="40" t="inlineStr">
+      <c r="E44" s="89" t="inlineStr">
         <is>
           <t>Year 1 (any quarter)</t>
         </is>
       </c>
-      <c r="F44" s="40" t="inlineStr">
+      <c r="F44" s="89" t="inlineStr">
         <is>
           <t>Global Experience</t>
         </is>
       </c>
-      <c r="G44" s="40" t="inlineStr">
+      <c r="G44" s="89" t="inlineStr">
         <is>
           <t>Varies</t>
         </is>
       </c>
-      <c r="H44" s="41" t="inlineStr">
+      <c r="H44" s="89" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="I44" s="40" t="inlineStr">
+      <c r="I44" s="89" t="inlineStr">
         <is>
           <t>Choose one: GMIX (4-wk immersion in 90+ countries), Global Seminars, Global Study Trips, STEP (Tsinghua), or Self-Directed Global Project.</t>
         </is>
       </c>
-      <c r="J44" s="40" t="inlineStr">
+      <c r="J44" s="89" t="inlineStr">
         <is>
           <t>Required global component</t>
+        </is>
+      </c>
+      <c r="K44" s="65" t="inlineStr">
+        <is>
+          <t>— (global immersion requirement; no direct online equivalent)</t>
+        </is>
+      </c>
+      <c r="L44" s="65" t="inlineStr">
+        <is>
+          <t>— (global immersion requirement; no direct online equivalent)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A35:A37"/>
     <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A40:A44"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A31:A34"/>
@@ -2789,7 +3394,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>Topic Coverage Matrix — which schools teach each topic in Year 1</t>
+          <t>Topic Coverage Matrix — which schools teach each topic in Year 1  | Free &amp; paid learning resources added to Master sheet (cols K–L)</t>
         </is>
       </c>
     </row>

--- a/m7_year1_master_by_topic.xlsx
+++ b/m7_year1_master_by_topic.xlsx
@@ -991,7 +991,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="n"/>
+      <c r="A5" s="7" t="n"/>
       <c r="B5" s="64" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -1048,7 +1048,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="n"/>
+      <c r="A6" s="7" t="n"/>
       <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1092,20 +1092,28 @@
       <c r="J6" s="64" t="inlineStr"/>
       <c r="K6" s="65" t="inlineStr">
         <is>
-          <t>Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Class Takeaways – Accounting Literacy (Prof. Ed deHaan) [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+ACCT 210 Syllabus 2019 (studocu.com/en-us/document/stanford-university/financial-accounting/acct-210-syllabus-2019/7696528)
+Stanford GSB Case Studies – free cases (gsb.stanford.edu/faculty-research/case-studies)
+★ GENERAL:
+Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
 MIT OCW Financial Accounting 15.515 (ocw.mit.edu/courses/15-515-financial-accounting-fall-2003/)
 Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)</t>
         </is>
       </c>
       <c r="L6" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+          <t>★ STANFORD OFFICIAL:
+Stanford Online MS&amp;E 240 Accounting for Managers &amp; Entrepreneurs (online.stanford.edu/courses/mse240-accounting-managers-and-entrepreneurs)
+★ OTHER PAID:
+HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1149,14 +1157,21 @@
       <c r="J7" s="64" t="inlineStr"/>
       <c r="K7" s="65" t="inlineStr">
         <is>
-          <t>Edspira – Managerial Accounting series (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Class Takeaways – Accounting Literacy (Prof. Ed deHaan) [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+Stanford GSB Case Studies – free cases (gsb.stanford.edu/faculty-research/case-studies)
+★ GENERAL:
+Edspira – Managerial Accounting series (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
 Farhat Accounting Lectures – Managerial Accounting (YT: search 'Farhat Lectures')
 Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)</t>
         </is>
       </c>
       <c r="L7" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+          <t>★ STANFORD OFFICIAL:
+Stanford Online MS&amp;E 240 Accounting for Managers &amp; Entrepreneurs (online.stanford.edu/courses/mse240-accounting-managers-and-entrepreneurs)
+★ OTHER PAID:
+HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
@@ -1224,7 +1239,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="n"/>
+      <c r="A9" s="7" t="n"/>
       <c r="B9" s="69" t="inlineStr">
         <is>
           <t>HBS</t>
@@ -1280,7 +1295,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="n"/>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="69" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -1341,7 +1356,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="69" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1385,14 +1400,23 @@
       <c r="J11" s="69" t="inlineStr"/>
       <c r="K11" s="65" t="inlineStr">
         <is>
-          <t>Aswath Damodaran – Valuation MBA Spring 2025 (YT: youtube.com/playlist?list=PLUkh9m2BorqkgpNyRpP-NL3BS4yvFabXk)
+          <t>★ STANFORD OFFICIAL:
+Anat Admati – FINANCE 332 Syllabus PDF (gsb-faculty.stanford.edu/anat-r-admati)
+All Else Equal Podcast – finance &amp; decision-making (gsb.stanford.edu/business-podcasts/all-else-equal-making-better-decisions)
+Stanford GSB Quick Study Videos – finance research (gsb.stanford.edu/business-videos/quick-study)
+★ GENERAL:
+Aswath Damodaran – Valuation MBA Spring 2025 (YT: youtube.com/playlist?list=PLUkh9m2BorqkgpNyRpP-NL3BS4yvFabXk)
 Patrick Boyle – On Finance (YT: youtube.com/@PBoyle)
 Corporate Finance Institute – CFI (YT: youtube.com/channel/UCGtbVv_ACgV7difdVZ92NMw)</t>
         </is>
       </c>
       <c r="L11" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
+          <t>★ STANFORD OFFICIAL:
+Stanford Online MS&amp;E 276 Entrepreneurial Management &amp; Finance (online.stanford.edu/courses/mse276-entrepreneurial-management-and-finance)
+Stanford LEAD Program ~$19,200 – covers financial valuation module (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
 Wharton Finance on Coursera – free audit / $49 cert (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
@@ -1463,7 +1487,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="66" t="n"/>
+      <c r="A13" s="7" t="n"/>
       <c r="B13" s="71" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -1523,7 +1547,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="n"/>
+      <c r="A14" s="7" t="n"/>
       <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1571,18 +1595,27 @@
       </c>
       <c r="K14" s="65" t="inlineStr">
         <is>
-          <t>Marginal Revolution University – Principles of Microeconomics (mru.org/courses/principles-of-microeconomics)
+          <t>★ STANFORD OFFICIAL:
+Stanford Coursera Game Theory – Matthew Jackson (free audit; coursera.org/learn/game-theory-1)
+Stanford Game Theory II – Advanced (free audit; coursera.org/learn/game-theory-2)
+Stanford edX Principles of Economics (free audit; edx.org/learn/economics/stanford-university-principles-of-economics)
+If/Then Podcast – economics &amp; pricing research episodes (gsb.stanford.edu/business-podcasts/if-then)
+★ GENERAL:
+Marginal Revolution University – Principles of Microeconomics (mru.org/courses/principles-of-microeconomics)
 Khan Academy Microeconomics (khanacademy.org/economics-finance-domain/microeconomics)</t>
         </is>
       </c>
       <c r="L14" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 – economics &amp; decision-making module (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="n"/>
+      <c r="A15" s="7" t="n"/>
       <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1630,19 +1663,26 @@
       </c>
       <c r="K15" s="65" t="inlineStr">
         <is>
-          <t>Marginal Revolution University – Principles of Macroeconomics (mru.org/courses/principles-of-macroeconomics)
+          <t>★ STANFORD OFFICIAL:
+Stanford edX Principles of Economics – covers macro (free audit; edx.org/learn/economics/stanford-university-principles-of-economics)
+If/Then Podcast – macro &amp; policy research episodes (gsb.stanford.edu/business-podcasts/if-then)
+★ GENERAL:
+Marginal Revolution University – Principles of Macroeconomics (mru.org/courses/principles-of-macroeconomics)
 Economics Explained (YT: youtube.com/c/EconomicsExplained)
 Khan Academy Macroeconomics (khanacademy.org/economics-finance-domain/macroeconomics)</t>
         </is>
       </c>
       <c r="L15" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="67" t="n"/>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1690,14 +1730,24 @@
       </c>
       <c r="K16" s="65" t="inlineStr">
         <is>
-          <t>Freakonomics Radio – business &amp; political economy episodes (freakonomics.com)
+          <t>★ STANFORD OFFICIAL:
+POLECON 239 Syllabus 2017 PDF – Saumitra Jha (web.stanford.edu/~saumitra/docs/POLECON239syllabus2017_1.pdf)
+Anat Admati – Finance &amp; Society Syllabus PDF (gsb-faculty.stanford.edu/anat-r-admati)
+Stanford GSB View From The Top – policy &amp; leadership talks [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+Stanford Social Innovation Review (ssir.org)
+Stanford eCorner – regulation &amp; innovation talks (ecorner.stanford.edu)
+★ GENERAL:
+Freakonomics Radio – business &amp; political economy episodes (freakonomics.com)
 HBS Cold Call Podcast – ethics &amp; policy cases (hbr.org/2019/04/podcast-cold-call)
 HBR IdeaCast Podcast (hbr.org/podcasts)</t>
         </is>
       </c>
       <c r="L16" s="65" t="inlineStr">
         <is>
-          <t>— (no direct HBS Online equivalent)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford Executive Program in Strategy &amp; Organization (gsb.stanford.edu/exec-ed/programs/executive-program-strategy-organization)
+★ OTHER PAID:
+— (no direct HBS Online equivalent)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1813,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="66" t="n"/>
+      <c r="A18" s="7" t="n"/>
       <c r="B18" s="73" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -1823,7 +1873,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="67" t="n"/>
+      <c r="A19" s="8" t="n"/>
       <c r="B19" s="73" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -1867,13 +1917,21 @@
       <c r="J19" s="73" t="inlineStr"/>
       <c r="K19" s="65" t="inlineStr">
         <is>
-          <t>HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Class Takeaways – Marketing &amp; consumer behavior episodes [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+If/Then Podcast – marketing research episodes (gsb.stanford.edu/business-podcasts/if-then)
+Stanford eCorner – go-to-market &amp; growth talks (ecorner.stanford.edu)
+★ GENERAL:
+HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
 Neil Patel – Digital Marketing Strategy (YT: youtube.com/neilpatel)</t>
         </is>
       </c>
       <c r="L19" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 – includes marketing module (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)
 Wharton Marketing on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
@@ -1939,7 +1997,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="66" t="n"/>
+      <c r="A21" s="7" t="n"/>
       <c r="B21" s="75" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -1999,7 +2057,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="67" t="n"/>
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="75" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2043,13 +2101,20 @@
       <c r="J22" s="75" t="inlineStr"/>
       <c r="K22" s="65" t="inlineStr">
         <is>
-          <t>MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
+          <t>★ STANFORD OFFICIAL:
+MS&amp;E 348 Course Page – related optimization content (web.stanford.edu/class/msande348/)
+Stanford GSB Quick Study Videos – operations research (gsb.stanford.edu/business-videos/quick-study)
+★ GENERAL:
+MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
 Wharton Operations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
       <c r="L22" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2184,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="66" t="n"/>
+      <c r="A24" s="7" t="n"/>
       <c r="B24" s="77" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -2176,7 +2241,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="66" t="n"/>
+      <c r="A25" s="7" t="n"/>
       <c r="B25" s="77" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2224,19 +2289,27 @@
       </c>
       <c r="K25" s="65" t="inlineStr">
         <is>
-          <t>StatQuest with Josh Starmer (YT: youtube.com/c/joshstarmer)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Class Takeaways – Data-Driven Decision Making (Prof. Mohsen Bayati) [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+All Else Equal Podcast – decision-making &amp; analytics (gsb.stanford.edu/business-podcasts/all-else-equal-making-better-decisions)
+★ GENERAL:
+StatQuest with Josh Starmer (YT: youtube.com/c/joshstarmer)
 Alex The Analyst (YT: youtube.com/@AlexTheAnalyst)
 Khan Academy Statistics (khanacademy.org/math/statistics-probability)</t>
         </is>
       </c>
       <c r="L25" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB ExecEd Data-Driven Decision Making (gsb.stanford.edu/exec-ed/programs/data-driven-decision-making)
+Stanford GSB Demystify Decision Making (gsb.stanford.edu/exec-ed/programs/demystify-decision-making)
+★ OTHER PAID:
+HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="66" t="n"/>
+      <c r="A26" s="7" t="n"/>
       <c r="B26" s="77" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2280,18 +2353,25 @@
       <c r="J26" s="77" t="inlineStr"/>
       <c r="K26" s="65" t="inlineStr">
         <is>
-          <t>StatQuest with Josh Starmer – ML/optimization concepts (YT: youtube.com/c/joshstarmer)
+          <t>★ STANFORD OFFICIAL:
+MS&amp;E 348 Course Page – decision trees, stochastic programming, Monte Carlo (web.stanford.edu/class/msande348/)
+Stanford edX – quantitative methods content (edx.org/school/stanfordonline)
+★ GENERAL:
+StatQuest with Josh Starmer – ML/optimization concepts (YT: youtube.com/c/joshstarmer)
 365 Data Science (YT: youtube.com/c/365DataScience)</t>
         </is>
       </c>
       <c r="L26" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Demystify Decision Making (gsb.stanford.edu/exec-ed/programs/demystify-decision-making)
+★ OTHER PAID:
+HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="67" t="n"/>
+      <c r="A27" s="8" t="n"/>
       <c r="B27" s="77" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2335,13 +2415,21 @@
       <c r="J27" s="77" t="inlineStr"/>
       <c r="K27" s="65" t="inlineStr">
         <is>
-          <t>HBR IdeaCast – Digital transformation episodes (hbr.org/podcasts)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB View From The Top – technology leadership talks [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+If/Then Podcast – AI &amp; technology research (gsb.stanford.edu/business-podcasts/if-then)
+Stanford eCorner – digital transformation &amp; platform talks (ecorner.stanford.edu)
+★ GENERAL:
+HBR IdeaCast – Digital transformation episodes (hbr.org/podcasts)
 Stanford GSB YouTube – technology strategy talks (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
         </is>
       </c>
       <c r="L27" s="65" t="inlineStr">
         <is>
-          <t>— (no direct HBS Online equivalent)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford Online MS&amp;E 280 Organizational Behavior (includes IT strategy module; online.stanford.edu/courses/mse280-organizational-behavior-evidence-action)
+★ OTHER PAID:
+— (no direct HBS Online equivalent)</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2496,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="66" t="n"/>
+      <c r="A29" s="7" t="n"/>
       <c r="B29" s="79" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -2469,7 +2557,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="67" t="n"/>
+      <c r="A30" s="8" t="n"/>
       <c r="B30" s="79" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2513,14 +2601,25 @@
       <c r="J30" s="79" t="inlineStr"/>
       <c r="K30" s="65" t="inlineStr">
         <is>
-          <t>Modern MBA (YT: youtube.com/c/ModernMBA)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB View From The Top [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+Think Fast Talk Smart Podcast – 200+ episodes on leadership &amp; communication (gsb.stanford.edu/business-podcasts/think-fast-talk-smart-podcast / fastersmarter.io)
+Jeffrey Pfeffer OB 377 Course Outline 2024 PDF (jeffreypfeffer.com/wp-content/uploads/2024/08/CourseOutline2024.pdf)
+Stanford eCorner – leadership &amp; scaling talks (ecorner.stanford.edu)
+★ GENERAL:
+Modern MBA (YT: youtube.com/c/ModernMBA)
 Stanford GSB YouTube – strategy talks (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)
 HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)</t>
         </is>
       </c>
       <c r="L30" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 – core strategic leadership focus (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+Stanford Online Discover Paths to Power ~$1,500 – Jeffrey Pfeffer (online.stanford.edu/courses/gsb-x0013-discover-paths-power)
+Stanford Executive Program in Strategy &amp; Organization (gsb.stanford.edu/exec-ed/programs/executive-program-strategy-organization)
+★ OTHER PAID:
+HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2687,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="66" t="n"/>
+      <c r="A32" s="7" t="n"/>
       <c r="B32" s="81" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -2645,7 +2744,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="66" t="n"/>
+      <c r="A33" s="7" t="n"/>
       <c r="B33" s="81" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2689,7 +2788,13 @@
       <c r="J33" s="81" t="inlineStr"/>
       <c r="K33" s="65" t="inlineStr">
         <is>
-          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+          <t>★ STANFORD OFFICIAL:
+Coursera Organizational Analysis – Stanford (free audit, 4.6★, 78k+ enrolled; coursera.org/learn/organizational-analysis)
+Stanford GSB View From The Top [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+Stanford GSB Class Takeaways – Team Management &amp; Humor in Business [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+Think Fast Talk Smart Podcast (gsb.stanford.edu/business-podcasts/think-fast-talk-smart-podcast)
+★ GENERAL:
+Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
 HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)
 Stanford GSB YouTube (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)
 TED Business (YT: youtube.com/c/TEDBusiness)</t>
@@ -2697,12 +2802,18 @@
       </c>
       <c r="L33" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford Online MS&amp;E 280 Organizational Behavior – Evidence in Action (Stanford credit; online.stanford.edu/courses/mse280-organizational-behavior-evidence-action)
+Stanford GSB Managing Teams for Innovation &amp; Success (gsb.stanford.edu/exec-ed/programs/managing-teams-innovation-success)
+Stanford Online Discover Paths to Power ~$1,500 (online.stanford.edu/courses/gsb-x0013-discover-paths-power)
+Stanford Online Influence &amp; Negotiation Strategies (online.stanford.edu/courses/gsb-x0007-influence-and-negotiation-strategies-program)
+★ OTHER PAID:
+HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="67" t="n"/>
+      <c r="A34" s="8" t="n"/>
       <c r="B34" s="81" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2746,13 +2857,21 @@
       <c r="J34" s="81" t="inlineStr"/>
       <c r="K34" s="65" t="inlineStr">
         <is>
-          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Class Takeaways – Talent &amp; Culture episodes [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+If/Then Podcast – future of work &amp; talent research (gsb.stanford.edu/business-podcasts/if-then)
+Stanford GSB Quick Study Videos – HR research (gsb.stanford.edu/business-videos/quick-study)
+★ GENERAL:
+Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
 HBR IdeaCast Podcast – people &amp; talent episodes (hbr.org/podcasts)</t>
         </is>
       </c>
       <c r="L34" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB Managing Teams for Innovation &amp; Success (gsb.stanford.edu/exec-ed/programs/managing-teams-innovation-success)
+★ OTHER PAID:
+HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2937,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="66" t="n"/>
+      <c r="A36" s="7" t="n"/>
       <c r="B36" s="83" t="inlineStr">
         <is>
           <t>HBS</t>
@@ -2878,7 +2997,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="n"/>
+      <c r="A37" s="8" t="n"/>
       <c r="B37" s="83" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -2922,14 +3041,22 @@
       <c r="J37" s="83" t="inlineStr"/>
       <c r="K37" s="65" t="inlineStr">
         <is>
-          <t>HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)
+          <t>★ STANFORD OFFICIAL:
+Stanford GSB View From The Top – values &amp; ethics episodes [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+Stanford GSB Class Takeaways – Leading with Values (Profs. Malhotra &amp; Shotts) [YT: youtube.com/playlist?list=PLxq_lXOUlvQCrEwiwPaUSJoUzIDTUnq2_]
+Stanford Social Innovation Review (ssir.org)
+★ GENERAL:
+HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)
 TED Business (YT: youtube.com/c/TEDBusiness)
 HBR IdeaCast Podcast (hbr.org/podcasts)</t>
         </is>
       </c>
       <c r="L37" s="65" t="inlineStr">
         <is>
-          <t>— (no direct HBS Online equivalent)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 – includes ethics &amp; values module (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+— (no direct HBS Online equivalent)</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3250,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="66" t="n"/>
+      <c r="A41" s="7" t="n"/>
       <c r="B41" s="89" t="inlineStr">
         <is>
           <t>HBS</t>
@@ -3181,7 +3308,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="66" t="n"/>
+      <c r="A42" s="7" t="n"/>
       <c r="B42" s="89" t="inlineStr">
         <is>
           <t>MIT Sloan</t>
@@ -3239,7 +3366,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="66" t="n"/>
+      <c r="A43" s="7" t="n"/>
       <c r="B43" s="89" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -3287,18 +3414,25 @@
       </c>
       <c r="K43" s="65" t="inlineStr">
         <is>
-          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+          <t>★ STANFORD OFFICIAL:
+Think Fast Talk Smart Podcast – 200+ communication &amp; leadership episodes (gsb.stanford.edu/business-podcasts/think-fast-talk-smart-podcast / fastersmarter.io)
+Stanford GSB View From The Top [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+★ GENERAL:
+Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
 Stanford GSB YouTube (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
         </is>
       </c>
       <c r="L43" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford Online Influence &amp; Negotiation Strategies (online.stanford.edu/courses/gsb-x0007-influence-and-negotiation-strategies-program)
+★ OTHER PAID:
+HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="67" t="n"/>
+      <c r="A44" s="8" t="n"/>
       <c r="B44" s="89" t="inlineStr">
         <is>
           <t>Stanford GSB</t>
@@ -3346,12 +3480,20 @@
       </c>
       <c r="K44" s="65" t="inlineStr">
         <is>
-          <t>— (global immersion requirement; no direct online equivalent)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford eCorner – global entrepreneurship &amp; emerging markets talks (ecorner.stanford.edu)
+Stanford Social Innovation Review – global development (ssir.org)
+Stanford GSB View From The Top – global leaders [YT: youtube.com/playlist?list=PLxq_lXOUlvQAwaY_9K4ZFH9Xdar9WzCaL]
+★ GENERAL:
+— (global immersion requirement; no direct online equivalent)</t>
         </is>
       </c>
       <c r="L44" s="65" t="inlineStr">
         <is>
-          <t>— (global immersion requirement; no direct online equivalent)</t>
+          <t>★ STANFORD OFFICIAL:
+Stanford LEAD Program ~$19,200 – global cohort &amp; virtual immersion (gsb.stanford.edu/exec-ed/programs/stanford-lead)
+★ OTHER PAID:
+— (global immersion requirement; no direct online equivalent)</t>
         </is>
       </c>
     </row>

--- a/m7_year1_master_by_topic.xlsx
+++ b/m7_year1_master_by_topic.xlsx
@@ -1035,14 +1035,24 @@
       <c r="J5" s="64" t="inlineStr"/>
       <c r="K5" s="65" t="inlineStr">
         <is>
-          <t>Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
+          <t>★ MIT OFFICIAL (OCW – FREE):
+MIT OCW 15.501 Intro to Financial &amp; Managerial Accounting – lecture notes, 7 problem sets + solutions, 3 exams + solutions (ocw.mit.edu/courses/15-501-introduction-to-financial-and-managerial-accounting-spring-2004/)
+MIT OCW 15.515 Financial Accounting – lecture notes, assignments (ocw.mit.edu/courses/15-515-financial-accounting-fall-2003/)
+MIT OCW Collection – MBA First-Semester Core (ocw.mit.edu/collections/sloan-mba-first-semester-core/)
+MIT Ideas Made to Matter – accounting &amp; finance articles (mitsloan.mit.edu/ideas-made-to-matter)
+★ GENERAL:
+Edspira (YT: youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg)
 MIT OCW Financial Accounting 15.515 (ocw.mit.edu/courses/15-515-financial-accounting-fall-2003/)
 Khan Academy Finance &amp; Accounting (khanacademy.org/economics-finance-domain/core-finance)</t>
         </is>
       </c>
       <c r="L5" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
+          <t>★ MIT OFFICIAL (PAID):
+MITx Financial Accounting on edX – free audit / ~$300 cert (edx.org/learn/financial-accounting/massachusetts-institute-of-technology-financial-accounting)
+MITx MicroMasters in Finance – includes Financial Accounting (edx.org/micromasters/mitx-finance)
+★ OTHER PAID:
+HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
@@ -1343,14 +1353,27 @@
       </c>
       <c r="K10" s="65" t="inlineStr">
         <is>
-          <t>Aswath Damodaran – Corporate Finance Full Course (YT: youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw)
+          <t>★ MIT OFFICIAL (OCW – FREE) — Crown Jewel:
+MIT OCW 15.401 Finance Theory I – FULL VIDEO LECTURES (all 12 modules, 90 min each), slides, recitation notes, problem sets + solutions, exams (ocw.mit.edu/courses/15-401-finance-theory-i-fall-2008/)
+YouTube Playlist – 15.401 Full Lectures by Prof. Andrew Lo (youtube.com/playlist?list=PLUl4u3cNGP63B2lDhyKOsImI7FjCf6eDW)
+Internet Archive backup: archive.org/details/MIT15.401F08
+Prof. Andrew Lo Teaching Page + 2018 syllabus (alo.mit.edu/teaching/)
+MIT OCW 15.481x Adaptive Markets – videos, problem sets (ocw.mit.edu/courses/15-481x-adaptive-markets-financial-market-dynamics-and-human-behavior-fall-2022/)
+★ GENERAL:
+Aswath Damodaran – Corporate Finance Full Course (YT: youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw)
 Patrick Boyle – On Finance (YT: youtube.com/@PBoyle)
 Corporate Finance Institute – CFI (YT: youtube.com/channel/UCGtbVv_ACgV7difdVZ92NMw)</t>
         </is>
       </c>
       <c r="L10" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
+          <t>★ MIT OFFICIAL (PAID):
+MITx Foundations of Modern Finance I – free audit / ~$300 cert (edx.org/learn/finance/massachusetts-institute-of-technology-foundations-of-modern-finance-i)
+MITx Foundations of Modern Finance II (edx.org/learn/finance/massachusetts-institute-of-technology-foundations-of-modern-finance-ii)
+MITx MicroMasters in Finance – 5-course program, graduate-level (edx.org/micromasters/mitx-finance)
+MIT ExecEd Fundamentals of Finance for Technical Executives (executive.mit.edu/course/fundamentals-of-finance-for-the-technical-executive/a056g00000URaMtAAL.html)
+★ OTHER PAID:
+HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)
 Wharton Finance on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
@@ -1535,14 +1558,22 @@
       </c>
       <c r="K13" s="65" t="inlineStr">
         <is>
-          <t>Marginal Revolution University – Microeconomics (mru.org)
+          <t>★ MIT OFFICIAL (OCW – FREE):
+MIT OCW 15.010 Economic Analysis for Business Decisions – full lecture notes, 6 homework sets + solutions, 6 years of final exams + solutions (ocw.mit.edu/courses/15-010-economic-analysis-for-business-decisions-fall-2004/)
+Covers: market definition, pricing strategy, oligopoly, game theory, auctions, antitrust, asymmetric information
+Textbook: Pindyck &amp; Rubinfeld Microeconomics (publicly referenced)
+★ GENERAL:
+Marginal Revolution University – Microeconomics (mru.org)
 Khan Academy Microeconomics (khanacademy.org/economics-finance-domain/microeconomics)
 Freakonomics Radio Podcast (freakonomics.com)</t>
         </is>
       </c>
       <c r="L13" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd Systems Thinking &amp; Complex Problem Solving (executive.mit.edu/course/understanding-and-solving-complex-business-problems/a046g00000PI9BcAAL.html)
+★ OTHER PAID:
+HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1892,24 @@
       </c>
       <c r="K18" s="65" t="inlineStr">
         <is>
-          <t>HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
+          <t>★ MIT OFFICIAL (FREE):
+Prof. John Hauser Faculty Page – 15.814 assignments, problem sets, pricing &amp; promotions exercises, 2018 syllabus PDF (mitmgmtfaculty.mit.edu/jhauser/course_materials/)
+Direct syllabus PDF: mit.edu/~hauser/Pages/Syllabus%2015.814%20Fall%202018%20May%2021.pdf
+MIT OCW 15.810 Marketing Management Fall 2015 – lecture notes, readings (ocw.mit.edu/courses/15-810-marketing-management-analytics-frameworks-and-applications-fall-2015/)
+MIT OCW 15.810 Marketing Management Fall 2010 – lecture notes, projects (ocw.mit.edu/courses/15-810-marketing-management-fall-2010/)
+MIT Ideas Made to Matter – marketing &amp; consumer behavior articles (mitsloan.mit.edu/ideas-made-to-matter)
+★ GENERAL:
+HubSpot Marketing YouTube + HubSpot Academy (youtube.com/user/HubSpot; academy.hubspot.com)
 Neil Patel – Digital Marketing Strategy (YT: youtube.com/neilpatel)
 Wharton Marketing on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
       <c r="L18" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)</t>
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd – Marketing &amp; Strategy programs (executive.mit.edu)
+★ OTHER PAID:
+HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)</t>
         </is>
       </c>
     </row>
@@ -2045,13 +2086,22 @@
       </c>
       <c r="K21" s="65" t="inlineStr">
         <is>
-          <t>MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
+          <t>★ MIT OFFICIAL (OCW – FREE):
+MIT OCW 15.761 Intro to Operations Management Spring 2013 – cases, simulation exercises, assignments (ocw.mit.edu/courses/15-761-introduction-to-operations-management-spring-2013/)
+MIT OCW 15.760b Intro to Operations Management Spring 2004 – full lecture notes PDFs (~19 lectures: process flow, Little's Law, inventory, queuing, supply chains) (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
+Textbook: Cachon &amp; Terwiesch Matching Supply with Demand (referenced)
+MIT Ideas Made to Matter – operations &amp; supply chain articles (mitsloan.mit.edu/ideas-made-to-matter)
+★ GENERAL:
+MIT OCW Intro to Operations Management 15.760B (ocw.mit.edu/courses/15-760b-introduction-to-operations-management-spring-2004/)
 Wharton Operations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
       <c r="L21" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd System Dynamics &amp; Business Dynamics (executive.mit.edu/course/business-dynamics/a056g00000URaMkAAL.html)
+★ OTHER PAID:
+HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)
 Wharton Operations on Coursera ~$49 cert</t>
         </is>
       </c>
@@ -2228,14 +2278,26 @@
       <c r="J24" s="77" t="inlineStr"/>
       <c r="K24" s="65" t="inlineStr">
         <is>
-          <t>StatQuest with Josh Starmer – Statistics &amp; ML (YT: youtube.com/c/joshstarmer)
+          <t>★ MIT OFFICIAL (OCW – FREE):
+MIT OCW 15.060 Data, Models &amp; Decisions Fall 2014 – syllabus, lecture summaries, 7 homework sets + solutions (probability, simulation, regression, linear optimization, discrete optimization) (ocw.mit.edu/courses/15-060-data-models-and-decisions-fall-2014/)
+MIT OCW 15.071 The Analytics Edge Spring 2017 – WITH VIDEO LECTURES; covers regression, trees, text analytics, optimization, visualization (ocw.mit.edu/courses/15-071-the-analytics-edge-spring-2017/)
+MIT OCW 15.063 Communicating With Data Summer 2003 (ocw.mit.edu/courses/15-063-communicating-with-data-summer-2003/)
+MIT Open Learning Library 15.481x Adaptive Markets – free interactive (openlearninglibrary.mit.edu/courses/course-v1:MITx+15.481x+1T2021/about)
+MIT Ideas Made to Matter – data &amp; AI articles (mitsloan.mit.edu/ideas-made-to-matter)
+Data Made to Matter Podcast (mitsloan.mit.edu/podcast)
+★ GENERAL:
+StatQuest with Josh Starmer – Statistics &amp; ML (YT: youtube.com/c/joshstarmer)
 Alex The Analyst (YT: youtube.com/@AlexTheAnalyst)
 Khan Academy Statistics &amp; Probability (khanacademy.org/math/statistics-probability)</t>
         </is>
       </c>
       <c r="L24" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)
+          <t>★ MIT OFFICIAL (PAID):
+MITx Mathematical Methods for Quantitative Finance – free audit (edx.org/micromasters/mitx-finance)
+MIT ExecEd Systems Thinking Courses (executive.mit.edu/systems-thinking)
+★ OTHER PAID:
+HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)
 HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
         </is>
       </c>
@@ -2544,14 +2606,24 @@
       </c>
       <c r="K29" s="65" t="inlineStr">
         <is>
-          <t>Modern MBA (YT: youtube.com/c/ModernMBA)
+          <t>★ MIT OFFICIAL (FREE):
+MIT Sloan 15.900 Official Syllabus PDF Fall 2022 – full session list, case list (Apple, Southwest, Zara, Netflix, Disney, Danaher) (mitsloan.mit.edu/sites/default/files/inline-files/Comp%20Strat%202022%20syllabus%2010%20AUG%2022%5B46%5D.pdf)
+MIT OCW 15.902 Strategic Management I – full lecture notes (Delta Model, Porter, RBV, competitive positioning) (ocw.mit.edu/courses/15-902-strategic-management-i-fall-2006/)
+MIT OCW 15.963 Advanced Strategy – lecture notes incl. '15.900 Review: Strategy Fundamentals' (ocw.mit.edu/courses/15-963-advanced-strategy-spring-2008/)
+MIT Sloan Management Review – strategy articles (sloanreview.mit.edu)
+MIT Ideas Made to Matter – strategy research (mitsloan.mit.edu/ideas-made-to-matter)
+★ GENERAL:
+Modern MBA (YT: youtube.com/c/ModernMBA)
 Acquired Podcast (acquired.fm)
 HBS Cold Call Podcast (hbr.org/2019/04/podcast-cold-call)</t>
         </is>
       </c>
       <c r="L29" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd Executive Program in Strategy &amp; Organization (executive.mit.edu)
+★ OTHER PAID:
+HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)
 Wharton Business Foundations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
@@ -2731,14 +2803,26 @@
       <c r="J32" s="81" t="inlineStr"/>
       <c r="K32" s="65" t="inlineStr">
         <is>
-          <t>Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
+          <t>★ MIT OFFICIAL (OCW – FREE):
+MIT OCW 15.311 Organizational Processes Fall 2003 – syllabus, readings list (org power, networks, culture, strategy design), assignments, team project description (ocw.mit.edu/courses/15-311-organizational-processes-fall-2003/)
+MIT OCW 15.317 Organizational Leadership &amp; Change Summer 2009 (ocw.mit.edu/courses/15-317-organizational-leadership-and-change-summer-2009/)
+Prof. John Sterman – Business Dynamics page &amp; textbook info (mitmgmtfaculty.mit.edu/jsterman/)
+MIT Sloan Management Review – org behavior &amp; leadership articles (sloanreview.mit.edu)
+Data Made to Matter Podcast (mitsloan.mit.edu/podcast)
+MITx Shaping Work of the Future – free audit on edX (edx.org/learn/human-resources/massachusetts-institute-of-technology-shaping-work-of-the-future)
+★ GENERAL:
+Simon Sinek YouTube (youtube.com/channel/UCBKbem_ewc4TVHBzE2Jp9Hg)
 HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)
 HBR IdeaCast Podcast (hbr.org/podcasts)</t>
         </is>
       </c>
       <c r="L32" s="65" t="inlineStr">
         <is>
-          <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd System Dynamics &amp; Business Dynamics (executive.mit.edu/course/business-dynamics/a056g00000URaMkAAL.html)
+MIT ExecEd Organizations &amp; Leadership courses (executive.mit.edu/organizations-and-leadership)
+★ OTHER PAID:
+HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)
 HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
         </is>
       </c>
@@ -3177,13 +3261,21 @@
       </c>
       <c r="K39" s="65" t="inlineStr">
         <is>
-          <t>TED Business – communication &amp; presentation talks (YT: youtube.com/c/TEDBusiness)
+          <t>★ MIT OFFICIAL (OCW – FREE):
+MIT OCW 15.280 Communication for Managers Fall 2016 – syllabus, readings, team presentation project, strategic communicator reflection assignment (ocw.mit.edu/courses/15-280-communication-for-managers-fall-2016/)
+MIT OCW 15.281 Advanced Communication for Leaders Spring 2016 (ocw.mit.edu/courses/sloan-school-of-management/15-281-advanced-communication-for-leaders-spring-2016/)
+MIT Ideas Made to Matter – communication &amp; leadership articles (mitsloan.mit.edu/ideas-made-to-matter)
+★ GENERAL:
+TED Business – communication &amp; presentation talks (YT: youtube.com/c/TEDBusiness)
 Stanford GSB YouTube – communication &amp; public speaking (youtube.com/channel/UCGwuxdEeCf0TIA2RbPOj-8g)</t>
         </is>
       </c>
       <c r="L39" s="65" t="inlineStr">
         <is>
-          <t>— (no direct HBS Online equivalent)</t>
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd Organizations &amp; Leadership courses (executive.mit.edu/organizations-and-leadership)
+★ OTHER PAID:
+— (no direct HBS Online equivalent)</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3448,22 @@
       </c>
       <c r="K42" s="65" t="inlineStr">
         <is>
-          <t>HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)</t>
+          <t>★ MIT OFFICIAL (FREE – closest proxies; 15.002 itself has no public materials):
+MIT OCW 15.317 Organizational Leadership &amp; Change Summer 2009 (ocw.mit.edu/courses/15-317-organizational-leadership-and-change-summer-2009/)
+MIT OCW 15.974 Practical Leadership Fall 2004 (ocw.mit.edu/courses/sloan-school-of-management/15-974-practical-leadership-fall-2004/)
+MIT Sloan Management Review – inclusion &amp; leadership articles (sloanreview.mit.edu)
+MITx Shaping Work of the Future – free audit on edX (edx.org/learn/human-resources/massachusetts-institute-of-technology-shaping-work-of-the-future)
+Sloanies Talking with Sloanies Podcast (mitsloan.mit.edu/alumni/sloanies-talking-sloanies)
+★ GENERAL:
+HarvardX Exercising Leadership – free audit on edX (edx.org/learn/leadership/harvard-university-exercising-leadership-foundational-principles)</t>
         </is>
       </c>
       <c r="L42" s="65" t="inlineStr">
         <is>
-          <t>— (immersive off-campus; no direct online equivalent)</t>
+          <t>★ MIT OFFICIAL (PAID):
+MIT ExecEd Organizations &amp; Leadership courses (executive.mit.edu/organizations-and-leadership)
+★ OTHER PAID:
+— (immersive off-campus; no direct online equivalent)</t>
         </is>
       </c>
     </row>

--- a/m7_year1_master_by_topic.xlsx
+++ b/m7_year1_master_by_topic.xlsx
@@ -65,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +147,11 @@
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -207,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -468,6 +473,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -835,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -850,6 +858,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -927,6 +936,11 @@
           <t>Paid Resources (HBS Online / Coursera)</t>
         </is>
       </c>
+      <c r="M3" s="90" t="inlineStr">
+        <is>
+          <t>⭐ Recommended Starter Course (Try This First)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
@@ -987,6 +1001,16 @@
         <is>
           <t>HBS Online Financial Accounting ~$1,750 (online.hbs.edu/courses/financial-accounting)
 HBS Online CORe Bundle ~$2,650 – includes Financial Accounting (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
+      <c r="M4" s="65" t="inlineStr">
+        <is>
+          <t>Edspira – Financial Accounting Playlist
+FREE · YouTube
+youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg
+Why: Prof. McLaughlin (PhD, CPA) makes the 'language of business' click in
+10-min bites. Sample 8–10 videos — accounting either grabs you or it doesn't.
+🎯 Careers if it clicks: CFO track, FP&amp;A, audit, financial analyst, controller.</t>
         </is>
       </c>
     </row>
@@ -1056,6 +1080,16 @@
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M5" s="65" t="inlineStr">
+        <is>
+          <t>Edspira – Financial Accounting Playlist
+FREE · YouTube
+youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg
+Why: Prof. McLaughlin (PhD, CPA) makes the 'language of business' click in
+10-min bites. Sample 8–10 videos — accounting either grabs you or it doesn't.
+🎯 Careers if it clicks: CFO track, FP&amp;A, audit, financial analyst, controller.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -1121,6 +1155,16 @@
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M6" s="65" t="inlineStr">
+        <is>
+          <t>Edspira – Financial Accounting Playlist
+FREE · YouTube
+youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg
+Why: Prof. McLaughlin (PhD, CPA) makes the 'language of business' click in
+10-min bites. Sample 8–10 videos — accounting either grabs you or it doesn't.
+🎯 Careers if it clicks: CFO track, FP&amp;A, audit, financial analyst, controller.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -1185,6 +1229,16 @@
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M7" s="65" t="inlineStr">
+        <is>
+          <t>Edspira – Financial Accounting Playlist
+FREE · YouTube
+youtube.com/channel/UCzRF-OFuv8os-bGzANpQGqg
+Why: Prof. McLaughlin (PhD, CPA) makes the 'language of business' click in
+10-min bites. Sample 8–10 videos — accounting either grabs you or it doesn't.
+🎯 Careers if it clicks: CFO track, FP&amp;A, audit, financial analyst, controller.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="68" t="inlineStr">
@@ -1247,6 +1301,18 @@
 HBS Online CORe Bundle ~$2,650 (online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Corporate Finance Full Course ⭐
+FREE · YouTube
+youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw
+Why: The 'Dean of Valuation' posts his entire NYU Stern MBA semester online.
+Highest-signal test — if the first 5 sessions energize you, finance is your field.
+Nothing freely available comes close in rigor or completeness.
+🎯 Careers if it clicks: Investment banking, PE/VC, equity research, asset
+management, corporate development, M&amp;A.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -1301,6 +1367,18 @@
       <c r="L9" s="65" t="inlineStr">
         <is>
           <t>HBS Online Leading with Finance ~$1,750 (online.hbs.edu/courses/leading-with-finance)</t>
+        </is>
+      </c>
+      <c r="M9" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Corporate Finance Full Course ⭐
+FREE · YouTube
+youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw
+Why: The 'Dean of Valuation' posts his entire NYU Stern MBA semester online.
+Highest-signal test — if the first 5 sessions energize you, finance is your field.
+Nothing freely available comes close in rigor or completeness.
+🎯 Careers if it clicks: Investment banking, PE/VC, equity research, asset
+management, corporate development, M&amp;A.</t>
         </is>
       </c>
     </row>
@@ -1377,6 +1455,18 @@
 Wharton Finance on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
+      <c r="M10" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Corporate Finance Full Course ⭐
+FREE · YouTube
+youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw
+Why: The 'Dean of Valuation' posts his entire NYU Stern MBA semester online.
+Highest-signal test — if the first 5 sessions energize you, finance is your field.
+Nothing freely available comes close in rigor or completeness.
+🎯 Careers if it clicks: Investment banking, PE/VC, equity research, asset
+management, corporate development, M&amp;A.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -1443,6 +1533,18 @@
 Wharton Finance on Coursera – free audit / $49 cert (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
+      <c r="M11" s="65" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran – Corporate Finance Full Course ⭐
+FREE · YouTube
+youtube.com/channel/UCLvnJL8htRR1T9cbSccaoVw
+Why: The 'Dean of Valuation' posts his entire NYU Stern MBA semester online.
+Highest-signal test — if the first 5 sessions energize you, finance is your field.
+Nothing freely available comes close in rigor or completeness.
+🎯 Careers if it clicks: Investment banking, PE/VC, equity research, asset
+management, corporate development, M&amp;A.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="70" t="inlineStr">
@@ -1506,6 +1608,18 @@
       <c r="L12" s="65" t="inlineStr">
         <is>
           <t>HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
+      <c r="M12" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Microeconomics
+FREE · mru.org
+mru.org/courses/principles-of-microeconomics
+Why: Built by Tyler Cowen (GMU professor) for self-learners — short, vivid,
+real-world examples. Tests whether thinking in incentives and trade-offs excites you.
+Add the Freakonomics Radio podcast (freakonomics.com) for applied macro flavor.
+🎯 Careers if it clicks: Economic consulting, policy/think tanks, central banking,
+pricing strategy, data economics.</t>
         </is>
       </c>
     </row>
@@ -1576,6 +1690,18 @@
 HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M13" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Microeconomics
+FREE · mru.org
+mru.org/courses/principles-of-microeconomics
+Why: Built by Tyler Cowen (GMU professor) for self-learners — short, vivid,
+real-world examples. Tests whether thinking in incentives and trade-offs excites you.
+Add the Freakonomics Radio podcast (freakonomics.com) for applied macro flavor.
+🎯 Careers if it clicks: Economic consulting, policy/think tanks, central banking,
+pricing strategy, data economics.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -1644,6 +1770,18 @@
 HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M14" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Microeconomics
+FREE · mru.org
+mru.org/courses/principles-of-microeconomics
+Why: Built by Tyler Cowen (GMU professor) for self-learners — short, vivid,
+real-world examples. Tests whether thinking in incentives and trade-offs excites you.
+Add the Freakonomics Radio podcast (freakonomics.com) for applied macro flavor.
+🎯 Careers if it clicks: Economic consulting, policy/think tanks, central banking,
+pricing strategy, data economics.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -1709,6 +1847,18 @@
 Stanford LEAD Program ~$19,200 (gsb.stanford.edu/exec-ed/programs/stanford-lead)
 ★ OTHER PAID:
 HBS Online Economics for Managers (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
+      <c r="M15" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Microeconomics
+FREE · mru.org
+mru.org/courses/principles-of-microeconomics
+Why: Built by Tyler Cowen (GMU professor) for self-learners — short, vivid,
+real-world examples. Tests whether thinking in incentives and trade-offs excites you.
+Add the Freakonomics Radio podcast (freakonomics.com) for applied macro flavor.
+🎯 Careers if it clicks: Economic consulting, policy/think tanks, central banking,
+pricing strategy, data economics.</t>
         </is>
       </c>
     </row>
@@ -1781,6 +1931,18 @@
 — (no direct HBS Online equivalent)</t>
         </is>
       </c>
+      <c r="M16" s="65" t="inlineStr">
+        <is>
+          <t>Marginal Revolution University – Principles of Microeconomics
+FREE · mru.org
+mru.org/courses/principles-of-microeconomics
+Why: Built by Tyler Cowen (GMU professor) for self-learners — short, vivid,
+real-world examples. Tests whether thinking in incentives and trade-offs excites you.
+Add the Freakonomics Radio podcast (freakonomics.com) for applied macro flavor.
+🎯 Careers if it clicks: Economic consulting, policy/think tanks, central banking,
+pricing strategy, data economics.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="72" t="inlineStr">
@@ -1840,6 +2002,19 @@
         <is>
           <t>HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)
 Wharton Marketing on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="M17" s="65" t="inlineStr">
+        <is>
+          <t>HubSpot Academy – Inbound Marketing Certification
+FREE · academy.hubspot.com
+academy.hubspot.com
+Why: Hands-on, immediately career-relevant. You'll know within hours if building
+campaigns and understanding customer behavior excites you.
+Upgrade path: HBS Online Digital Marketing Strategy (~$1,750) with Prof. Sunil
+Gupta for the strategic/brand layer.
+🎯 Careers if it clicks: Brand management, growth marketing, product marketing,
+digital strategy, CMO track.</t>
         </is>
       </c>
     </row>
@@ -1912,6 +2087,19 @@
 HBS Online Digital Marketing Strategy ~$1,750 (online.hbs.edu/courses/digital-marketing-strategy)</t>
         </is>
       </c>
+      <c r="M18" s="65" t="inlineStr">
+        <is>
+          <t>HubSpot Academy – Inbound Marketing Certification
+FREE · academy.hubspot.com
+academy.hubspot.com
+Why: Hands-on, immediately career-relevant. You'll know within hours if building
+campaigns and understanding customer behavior excites you.
+Upgrade path: HBS Online Digital Marketing Strategy (~$1,750) with Prof. Sunil
+Gupta for the strategic/brand layer.
+🎯 Careers if it clicks: Brand management, growth marketing, product marketing,
+digital strategy, CMO track.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1976,6 +2164,19 @@
 Wharton Marketing on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
+      <c r="M19" s="65" t="inlineStr">
+        <is>
+          <t>HubSpot Academy – Inbound Marketing Certification
+FREE · academy.hubspot.com
+academy.hubspot.com
+Why: Hands-on, immediately career-relevant. You'll know within hours if building
+campaigns and understanding customer behavior excites you.
+Upgrade path: HBS Online Digital Marketing Strategy (~$1,750) with Prof. Sunil
+Gupta for the strategic/brand layer.
+🎯 Careers if it clicks: Brand management, growth marketing, product marketing,
+digital strategy, CMO track.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="74" t="inlineStr">
@@ -2034,6 +2235,18 @@
         <is>
           <t>HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)
 Wharton Operations on Coursera ~$49 cert (coursera.org/specializations/wharton-business-foundations)</t>
+        </is>
+      </c>
+      <c r="M20" s="65" t="inlineStr">
+        <is>
+          <t>MIT OCW 15.761 – Introduction to Operations Management
+FREE · MIT OpenCourseWare
+ocw.mit.edu/courses/15-761-introduction-to-operations-management-spring-2013/
+Why: Supply-chain simulations let you do the work, not just read about it.
+Reveals quickly if optimizing systems and processes is your thing.
+Alternatively: MIT OCW 15.760b (2004 version) for more lecture notes.
+🎯 Careers if it clicks: Supply chain, operations management, consulting,
+manufacturing, logistics, procurement.</t>
         </is>
       </c>
     </row>
@@ -2105,6 +2318,18 @@
 Wharton Operations on Coursera ~$49 cert</t>
         </is>
       </c>
+      <c r="M21" s="65" t="inlineStr">
+        <is>
+          <t>MIT OCW 15.761 – Introduction to Operations Management
+FREE · MIT OpenCourseWare
+ocw.mit.edu/courses/15-761-introduction-to-operations-management-spring-2013/
+Why: Supply-chain simulations let you do the work, not just read about it.
+Reveals quickly if optimizing systems and processes is your thing.
+Alternatively: MIT OCW 15.760b (2004 version) for more lecture notes.
+🎯 Careers if it clicks: Supply chain, operations management, consulting,
+manufacturing, logistics, procurement.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -2167,6 +2392,18 @@
 HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
         </is>
       </c>
+      <c r="M22" s="65" t="inlineStr">
+        <is>
+          <t>MIT OCW 15.761 – Introduction to Operations Management
+FREE · MIT OpenCourseWare
+ocw.mit.edu/courses/15-761-introduction-to-operations-management-spring-2013/
+Why: Supply-chain simulations let you do the work, not just read about it.
+Reveals quickly if optimizing systems and processes is your thing.
+Alternatively: MIT OCW 15.760b (2004 version) for more lecture notes.
+🎯 Careers if it clicks: Supply chain, operations management, consulting,
+manufacturing, logistics, procurement.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="76" t="inlineStr">
@@ -2230,6 +2467,18 @@
         <is>
           <t>HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)
 HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
+      <c r="M23" s="65" t="inlineStr">
+        <is>
+          <t>Alex The Analyst – Data Analyst Bootcamp ⭐
+FREE · YouTube
+youtube.com/@AlexTheAnalyst
+Why: Career-shaped from day one: SQL → Python → Power BI → portfolio.
+Quickly reveals if working with data day-to-day clicks for you.
+Pair with StatQuest (youtube.com/c/joshstarmer) if the ML/AI layer pulls you deeper.
+🎯 Careers if it clicks: Data analyst, business intelligence, data science,
+analytics consulting, AI product roles.</t>
         </is>
       </c>
     </row>
@@ -2301,6 +2550,18 @@
 HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
         </is>
       </c>
+      <c r="M24" s="65" t="inlineStr">
+        <is>
+          <t>Alex The Analyst – Data Analyst Bootcamp ⭐
+FREE · YouTube
+youtube.com/@AlexTheAnalyst
+Why: Career-shaped from day one: SQL → Python → Power BI → portfolio.
+Quickly reveals if working with data day-to-day clicks for you.
+Pair with StatQuest (youtube.com/c/joshstarmer) if the ML/AI layer pulls you deeper.
+🎯 Careers if it clicks: Data analyst, business intelligence, data science,
+analytics consulting, AI product roles.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -2369,6 +2630,18 @@
 HBS Online Business Analytics (part of CORe ~$2,650; online.hbs.edu/courses/core)</t>
         </is>
       </c>
+      <c r="M25" s="65" t="inlineStr">
+        <is>
+          <t>Alex The Analyst – Data Analyst Bootcamp ⭐
+FREE · YouTube
+youtube.com/@AlexTheAnalyst
+Why: Career-shaped from day one: SQL → Python → Power BI → portfolio.
+Quickly reveals if working with data day-to-day clicks for you.
+Pair with StatQuest (youtube.com/c/joshstarmer) if the ML/AI layer pulls you deeper.
+🎯 Careers if it clicks: Data analyst, business intelligence, data science,
+analytics consulting, AI product roles.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -2429,6 +2702,18 @@
 Stanford GSB Demystify Decision Making (gsb.stanford.edu/exec-ed/programs/demystify-decision-making)
 ★ OTHER PAID:
 HBS Online Data Science &amp; AI for Decision Making (online.hbs.edu/courses/data-science-ai-decision-making)</t>
+        </is>
+      </c>
+      <c r="M26" s="65" t="inlineStr">
+        <is>
+          <t>Alex The Analyst – Data Analyst Bootcamp ⭐
+FREE · YouTube
+youtube.com/@AlexTheAnalyst
+Why: Career-shaped from day one: SQL → Python → Power BI → portfolio.
+Quickly reveals if working with data day-to-day clicks for you.
+Pair with StatQuest (youtube.com/c/joshstarmer) if the ML/AI layer pulls you deeper.
+🎯 Careers if it clicks: Data analyst, business intelligence, data science,
+analytics consulting, AI product roles.</t>
         </is>
       </c>
     </row>
@@ -2494,6 +2779,18 @@
 — (no direct HBS Online equivalent)</t>
         </is>
       </c>
+      <c r="M27" s="65" t="inlineStr">
+        <is>
+          <t>Alex The Analyst – Data Analyst Bootcamp ⭐
+FREE · YouTube
+youtube.com/@AlexTheAnalyst
+Why: Career-shaped from day one: SQL → Python → Power BI → portfolio.
+Quickly reveals if working with data day-to-day clicks for you.
+Pair with StatQuest (youtube.com/c/joshstarmer) if the ML/AI layer pulls you deeper.
+🎯 Careers if it clicks: Data analyst, business intelligence, data science,
+analytics consulting, AI product roles.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="78" t="inlineStr">
@@ -2554,6 +2851,19 @@
         <is>
           <t>HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)
 HBS Online Core Business Essentials ~$2,650 – includes Strategy module (online.hbs.edu/courses/core)</t>
+        </is>
+      </c>
+      <c r="M28" s="65" t="inlineStr">
+        <is>
+          <t>Modern MBA – Company Case Studies ⭐
+FREE · YouTube
+youtube.com/c/ModernMBA
+Why: Emmy-quality 40-min deep-dives on real companies (Apple, Netflix, LVMH…).
+The closest free equivalent to the HBS case method. If you binge these,
+strategy is your field. Pair with the Acquired Podcast (acquired.fm) for
+narrative-style company histories.
+🎯 Careers if it clicks: Management consulting (MBB), corporate strategy,
+BizOps, M&amp;A, general management.</t>
         </is>
       </c>
     </row>
@@ -2627,6 +2937,19 @@
 Wharton Business Foundations on Coursera – free audit (coursera.org/specializations/wharton-business-foundations)</t>
         </is>
       </c>
+      <c r="M29" s="65" t="inlineStr">
+        <is>
+          <t>Modern MBA – Company Case Studies ⭐
+FREE · YouTube
+youtube.com/c/ModernMBA
+Why: Emmy-quality 40-min deep-dives on real companies (Apple, Netflix, LVMH…).
+The closest free equivalent to the HBS case method. If you binge these,
+strategy is your field. Pair with the Acquired Podcast (acquired.fm) for
+narrative-style company histories.
+🎯 Careers if it clicks: Management consulting (MBB), corporate strategy,
+BizOps, M&amp;A, general management.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -2694,6 +3017,19 @@
 HBS Online Disruptive Strategy ~$1,949 (online.hbs.edu/courses/disruptive-strategy)</t>
         </is>
       </c>
+      <c r="M30" s="65" t="inlineStr">
+        <is>
+          <t>Modern MBA – Company Case Studies ⭐
+FREE · YouTube
+youtube.com/c/ModernMBA
+Why: Emmy-quality 40-min deep-dives on real companies (Apple, Netflix, LVMH…).
+The closest free equivalent to the HBS case method. If you binge these,
+strategy is your field. Pair with the Acquired Podcast (acquired.fm) for
+narrative-style company histories.
+🎯 Careers if it clicks: Management consulting (MBB), corporate strategy,
+BizOps, M&amp;A, general management.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="80" t="inlineStr">
@@ -2755,6 +3091,18 @@
         <is>
           <t>HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)
 HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
+        </is>
+      </c>
+      <c r="M31" s="65" t="inlineStr">
+        <is>
+          <t>Coursera – Organizational Analysis (Stanford University)
+FREE audit · coursera.org
+coursera.org/learn/organizational-analysis
+Why: A genuine Stanford academic course (4.6★, 78,000+ learners).
+Tests whether the theory of how organizations and people behave fascinates
+you — beyond 'leadership is inspiring' to the real science behind it.
+🎯 Careers if it clicks: HR / People leadership, org design, talent,
+executive coaching, organizational consulting.</t>
         </is>
       </c>
     </row>
@@ -2826,6 +3174,18 @@
 HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
         </is>
       </c>
+      <c r="M32" s="65" t="inlineStr">
+        <is>
+          <t>Coursera – Organizational Analysis (Stanford University)
+FREE audit · coursera.org
+coursera.org/learn/organizational-analysis
+Why: A genuine Stanford academic course (4.6★, 78,000+ learners).
+Tests whether the theory of how organizations and people behave fascinates
+you — beyond 'leadership is inspiring' to the real science behind it.
+🎯 Careers if it clicks: HR / People leadership, org design, talent,
+executive coaching, organizational consulting.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -2895,6 +3255,18 @@
 HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
         </is>
       </c>
+      <c r="M33" s="65" t="inlineStr">
+        <is>
+          <t>Coursera – Organizational Analysis (Stanford University)
+FREE audit · coursera.org
+coursera.org/learn/organizational-analysis
+Why: A genuine Stanford academic course (4.6★, 78,000+ learners).
+Tests whether the theory of how organizations and people behave fascinates
+you — beyond 'leadership is inspiring' to the real science behind it.
+🎯 Careers if it clicks: HR / People leadership, org design, talent,
+executive coaching, organizational consulting.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -2958,6 +3330,18 @@
 HBS Online Management Essentials ~$1,750 (online.hbs.edu/courses/management-essentials)</t>
         </is>
       </c>
+      <c r="M34" s="65" t="inlineStr">
+        <is>
+          <t>Coursera – Organizational Analysis (Stanford University)
+FREE audit · coursera.org
+coursera.org/learn/organizational-analysis
+Why: A genuine Stanford academic course (4.6★, 78,000+ learners).
+Tests whether the theory of how organizations and people behave fascinates
+you — beyond 'leadership is inspiring' to the real science behind it.
+🎯 Careers if it clicks: HR / People leadership, org design, talent,
+executive coaching, organizational consulting.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="82" t="inlineStr">
@@ -3019,6 +3403,19 @@
           <t>HBS Online Negotiation Mastery ~$1,850 (online.hbs.edu/courses/negotiation)</t>
         </is>
       </c>
+      <c r="M35" s="65" t="inlineStr">
+        <is>
+          <t>Michael Sandel – Justice (Harvard University)
+FREE · YouTube / justiceharvard.org
+justiceharvard.org
+Why: Harvard's legendary ethics course — the best free test of whether
+moral reasoning genuinely grips you. For the business ethics angle, browse
+Stanford Social Innovation Review (ssir.org) — free articles on ESG,
+stakeholder capitalism, and corporate accountability.
+🎯 Careers if it clicks: ESG / sustainability, corporate responsibility,
+compliance, social enterprise, impact investing.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -3077,6 +3474,19 @@
       <c r="L36" s="65" t="inlineStr">
         <is>
           <t>— (no direct HBS Online equivalent)</t>
+        </is>
+      </c>
+      <c r="M36" s="65" t="inlineStr">
+        <is>
+          <t>Michael Sandel – Justice (Harvard University)
+FREE · YouTube / justiceharvard.org
+justiceharvard.org
+Why: Harvard's legendary ethics course — the best free test of whether
+moral reasoning genuinely grips you. For the business ethics angle, browse
+Stanford Social Innovation Review (ssir.org) — free articles on ESG,
+stakeholder capitalism, and corporate accountability.
+🎯 Careers if it clicks: ESG / sustainability, corporate responsibility,
+compliance, social enterprise, impact investing.</t>
         </is>
       </c>
     </row>
@@ -3143,6 +3553,19 @@
 — (no direct HBS Online equivalent)</t>
         </is>
       </c>
+      <c r="M37" s="65" t="inlineStr">
+        <is>
+          <t>Michael Sandel – Justice (Harvard University)
+FREE · YouTube / justiceharvard.org
+justiceharvard.org
+Why: Harvard's legendary ethics course — the best free test of whether
+moral reasoning genuinely grips you. For the business ethics angle, browse
+Stanford Social Innovation Review (ssir.org) — free articles on ESG,
+stakeholder capitalism, and corporate accountability.
+🎯 Careers if it clicks: ESG / sustainability, corporate responsibility,
+compliance, social enterprise, impact investing.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="84" t="inlineStr">
@@ -3205,6 +3628,18 @@
       <c r="L38" s="65" t="inlineStr">
         <is>
           <t>HBS Online Entrepreneurship Essentials ~$1,850 (online.hbs.edu/courses/entrepreneurship-essentials)</t>
+        </is>
+      </c>
+      <c r="M38" s="65" t="inlineStr">
+        <is>
+          <t>Y Combinator – Startup School ⭐
+FREE · Structured Curriculum
+startupschool.org/curriculum
+Why: Taught by YC partners who funded Airbnb, Stripe, Dropbox, Coinbase.
+Dense, practical, zero fluff. You'll know within the first 3 sessions
+whether the founder path actually calls you.
+🎯 Careers if it clicks: Founder, early startup operator, VC/angel investing,
+product management, intrapreneurship.</t>
         </is>
       </c>
     </row>
@@ -3278,6 +3713,20 @@
 — (no direct HBS Online equivalent)</t>
         </is>
       </c>
+      <c r="M39" s="65" t="inlineStr">
+        <is>
+          <t>Think Fast, Talk Smart – Podcast (Stanford GSB)
+FREE · 200+ episodes
+gsb.stanford.edu/business-podcasts/think-fast-talk-smart-podcast
+fastersmarter.io
+Why: Matt Abrahams (Stanford GSB) covers communication anxiety, impromptu
+speaking, persuasion, negotiation presence. Immediately applicable.
+Note: Communication is a career multiplier, not a standalone field — it
+compounds every other career path you choose.
+🎯 Where it helps most: Leadership, consulting, sales, investor relations,
+any exec-track role.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="88" t="inlineStr">
@@ -3338,6 +3787,20 @@
       <c r="L40" s="65" t="inlineStr">
         <is>
           <t>— (experiential program; no direct online equivalent)</t>
+        </is>
+      </c>
+      <c r="M40" s="65" t="inlineStr">
+        <is>
+          <t>Stanford eCorner – Entrepreneurial Thought Leaders Series
+FREE · 2,000+ videos
+ecorner.stanford.edu
+youtube.com/@ecorner
+Why: The best free taste of global business, cross-border entrepreneurship,
+and international strategy. Guests include founders, VCs, and operators from
+90+ countries. Experiential learning has no true online substitute, but
+eCorner's global founder stories give you the flavor of international careers.
+🎯 Careers if it clicks: International business development, global strategy,
+cross-border M&amp;A, emerging markets, development finance.</t>
         </is>
       </c>
     </row>
@@ -3396,6 +3859,20 @@
       <c r="L41" s="65" t="inlineStr">
         <is>
           <t>— (experiential / global immersion; no direct online equivalent)</t>
+        </is>
+      </c>
+      <c r="M41" s="65" t="inlineStr">
+        <is>
+          <t>Stanford eCorner – Entrepreneurial Thought Leaders Series
+FREE · 2,000+ videos
+ecorner.stanford.edu
+youtube.com/@ecorner
+Why: The best free taste of global business, cross-border entrepreneurship,
+and international strategy. Guests include founders, VCs, and operators from
+90+ countries. Experiential learning has no true online substitute, but
+eCorner's global founder stories give you the flavor of international careers.
+🎯 Careers if it clicks: International business development, global strategy,
+cross-border M&amp;A, emerging markets, development finance.</t>
         </is>
       </c>
     </row>
@@ -3466,6 +3943,20 @@
 — (immersive off-campus; no direct online equivalent)</t>
         </is>
       </c>
+      <c r="M42" s="65" t="inlineStr">
+        <is>
+          <t>Stanford eCorner – Entrepreneurial Thought Leaders Series
+FREE · 2,000+ videos
+ecorner.stanford.edu
+youtube.com/@ecorner
+Why: The best free taste of global business, cross-border entrepreneurship,
+and international strategy. Guests include founders, VCs, and operators from
+90+ countries. Experiential learning has no true online substitute, but
+eCorner's global founder stories give you the flavor of international careers.
+🎯 Careers if it clicks: International business development, global strategy,
+cross-border M&amp;A, emerging markets, development finance.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -3532,6 +4023,20 @@
 HBS Online Leadership Principles ~$1,850 (online.hbs.edu/courses/leadership-principles)</t>
         </is>
       </c>
+      <c r="M43" s="65" t="inlineStr">
+        <is>
+          <t>Stanford eCorner – Entrepreneurial Thought Leaders Series
+FREE · 2,000+ videos
+ecorner.stanford.edu
+youtube.com/@ecorner
+Why: The best free taste of global business, cross-border entrepreneurship,
+and international strategy. Guests include founders, VCs, and operators from
+90+ countries. Experiential learning has no true online substitute, but
+eCorner's global founder stories give you the flavor of international careers.
+🎯 Careers if it clicks: International business development, global strategy,
+cross-border M&amp;A, emerging markets, development finance.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
@@ -3596,6 +4101,20 @@
 Stanford LEAD Program ~$19,200 – global cohort &amp; virtual immersion (gsb.stanford.edu/exec-ed/programs/stanford-lead)
 ★ OTHER PAID:
 — (global immersion requirement; no direct online equivalent)</t>
+        </is>
+      </c>
+      <c r="M44" s="65" t="inlineStr">
+        <is>
+          <t>Stanford eCorner – Entrepreneurial Thought Leaders Series
+FREE · 2,000+ videos
+ecorner.stanford.edu
+youtube.com/@ecorner
+Why: The best free taste of global business, cross-border entrepreneurship,
+and international strategy. Guests include founders, VCs, and operators from
+90+ countries. Experiential learning has no true online substitute, but
+eCorner's global founder stories give you the flavor of international careers.
+🎯 Careers if it clicks: International business development, global strategy,
+cross-border M&amp;A, emerging markets, development finance.</t>
         </is>
       </c>
     </row>
